--- a/KT Compliance.xlsx
+++ b/KT Compliance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://powerschoolgroup-my.sharepoint.com/personal/prabha_parthasarathy_powerschool_com/Documents/GPM/2026/KT 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="580" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2DAB563-F193-40DC-9CF3-01E2453E8E3B}"/>
+  <xr:revisionPtr revIDLastSave="605" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F9C925D-D582-43D3-9E0A-C0313C2C8678}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B7FEA37-02A6-41FF-9931-0A86E2A764FA}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$O$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$P$70</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="173">
   <si>
     <t>Product Area</t>
   </si>
@@ -92,6 +92,9 @@
     <t>Readiness Score</t>
   </si>
   <si>
+    <t>Target date</t>
+  </si>
+  <si>
     <t>Pending Items</t>
   </si>
   <si>
@@ -201,7 +204,7 @@
     <t>Chintan</t>
   </si>
   <si>
-    <t>Jason *</t>
+    <t>Jason*</t>
   </si>
   <si>
     <t>In process</t>
@@ -213,7 +216,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Jason is leading the state calls.</t>
+    <t xml:space="preserve">Jason leading calls </t>
   </si>
   <si>
     <t>SK</t>
@@ -232,6 +235,18 @@
   </si>
   <si>
     <t>WY</t>
+  </si>
+  <si>
+    <t>NA / Turab</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Turab-Jason</t>
+  </si>
+  <si>
+    <t>Jason in all state calls.</t>
   </si>
   <si>
     <t>GA</t>
@@ -515,9 +530,6 @@
     <t>Completed handover. FG meetings handled by US PM</t>
   </si>
   <si>
-    <t xml:space="preserve">Jason leading calls </t>
-  </si>
-  <si>
     <t>CT</t>
   </si>
   <si>
@@ -568,9 +580,6 @@
   </si>
   <si>
     <t>NE</t>
-  </si>
-  <si>
-    <t>Jason*</t>
   </si>
   <si>
     <t>Day  to Day Backlog management and sprint planning. Customer Introduction</t>
@@ -689,7 +698,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -722,6 +731,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1075,25 +1087,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
-  <dimension ref="A1:O70"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="8.85546875" style="3"/>
     <col min="4" max="4" width="19" style="11" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25" style="3" customWidth="1"/>
-    <col min="8" max="8" width="21.85546875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.85546875" style="3"/>
-    <col min="14" max="14" width="28.28515625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="3"/>
+    <col min="5" max="6" width="10.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17" style="3" customWidth="1"/>
+    <col min="8" max="8" width="25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.85546875" style="3"/>
+    <col min="15" max="15" width="28.28515625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16.140625" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="8" customFormat="1" ht="144.75">
+    <row r="1" spans="1:16" s="8" customFormat="1" ht="144.75">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1133,1774 +1146,1821 @@
       <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" hidden="1">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="29.25">
+      <c r="I2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="29.25" hidden="1">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="29.25" hidden="1">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="O3" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="29.25">
-      <c r="A4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
-      <c r="O4" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" hidden="1">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
       </c>
-      <c r="O5" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="57.75">
+      <c r="P5" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="57.75" hidden="1">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" s="3">
         <v>80</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="29.25">
+      <c r="P6" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="29.25">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3">
         <v>90</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>40</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="L7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P7" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" hidden="1">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" hidden="1">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="29.25">
+        <v>19</v>
+      </c>
+      <c r="P9" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="29.25" hidden="1">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="29.25">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" s="3">
         <v>100</v>
       </c>
-      <c r="O11" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="57.75">
+      <c r="F11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="P11" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="57.75" hidden="1">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" s="3">
         <v>90</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>22</v>
+      <c r="G12" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="O12" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="57.75">
+        <v>23</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P12" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="57.75" hidden="1">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" s="3">
         <v>100</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O13" s="4">
+      <c r="G13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P13" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16" hidden="1">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>65</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" hidden="1">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
       </c>
-      <c r="O15" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="29.25">
+      <c r="P15" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="29.25" hidden="1">
       <c r="A16" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>65</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" hidden="1">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="P17" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" hidden="1">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="3">
         <v>100</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O18" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="57.75">
+      <c r="G18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P18" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="57.75" hidden="1">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" s="3">
         <v>100</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O19" s="4">
+      <c r="G19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P19" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="57.75">
+    <row r="20" spans="1:16" ht="57.75" hidden="1">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" s="5">
         <v>0.9</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>24</v>
+      <c r="F20" s="5"/>
+      <c r="G20" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O20" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>25</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P20" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" hidden="1">
       <c r="A21" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="29.25">
+        <v>19</v>
+      </c>
+      <c r="P21" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="29.25" hidden="1">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="G22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>84</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" hidden="1">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="159">
+        <v>65</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="159" hidden="1">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="3">
         <v>90</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O24" s="4">
+      <c r="G24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="P24" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="29.25">
+    <row r="25" spans="1:16" ht="29.25" hidden="1">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="G25" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="57.75">
+        <v>84</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="57.75" hidden="1">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O26" s="4">
+      <c r="G26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P26" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:16" hidden="1">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E27" s="3">
         <v>100</v>
       </c>
-      <c r="O27" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="P27" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" hidden="1">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E28" s="3">
         <v>100</v>
       </c>
-      <c r="O28" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="P28" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" hidden="1">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29" s="3">
         <v>100</v>
       </c>
-      <c r="O29" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="P29" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" hidden="1">
       <c r="A30" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O30" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="43.5">
+        <v>19</v>
+      </c>
+      <c r="P30" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="43.5" hidden="1">
       <c r="A31" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E31" s="5">
         <v>0.5</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="F31" s="5"/>
       <c r="G31" s="3" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O31" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="29.25">
+        <v>25</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P31" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="29.25" hidden="1">
       <c r="A32" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O32" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="43.5">
+        <v>25</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P32" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="43.5" hidden="1">
       <c r="A33" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E33" s="3">
         <v>20</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O33" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="29.25">
+      <c r="G33" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P33" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="29.25" hidden="1">
       <c r="A34" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="O34" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="29.25">
+        <v>82</v>
+      </c>
+      <c r="P34" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="29.25" hidden="1">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="O35" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="57.75">
+        <v>82</v>
+      </c>
+      <c r="P35" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="57.75" hidden="1">
       <c r="A36" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E36" s="3">
         <v>100</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>111</v>
+      <c r="G36" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="O36" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="29.25">
+        <v>116</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P36" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="29.25" hidden="1">
       <c r="A37" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E37" s="3">
         <v>0</v>
       </c>
-      <c r="O37" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="57.75">
+      <c r="P37" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="57.75" hidden="1">
       <c r="A38" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E38" s="3">
         <v>80</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O38" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="57.75">
+      <c r="G38" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="P38" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="57.75" hidden="1">
       <c r="A39" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E39" s="3">
         <v>100</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O39" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="57.75">
+      <c r="G39" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="P39" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="57.75" hidden="1">
       <c r="A40" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E40" s="3">
         <v>100</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P40" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="43.5" hidden="1">
+      <c r="A41" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="N40" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="O40" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="43.5">
-      <c r="A41" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="D41" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="O41" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="87">
+      <c r="G41" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="P41" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="87" hidden="1">
       <c r="A42" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42" s="3">
         <v>80</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="O42" s="4">
+      <c r="G42" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P42" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="29.25">
+    <row r="43" spans="1:16" ht="29.25" hidden="1">
       <c r="A43" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C43" s="1"/>
-      <c r="O43" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="29.25">
+      <c r="P43" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="29.25" hidden="1">
       <c r="A44" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E44" s="3">
         <v>100</v>
       </c>
-      <c r="O44" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="29.25">
+      <c r="P44" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="29.25" hidden="1">
       <c r="A45" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="O45" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="29.25">
+        <v>133</v>
+      </c>
+      <c r="P45" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="29.25" hidden="1">
       <c r="A46" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C46" s="1"/>
-      <c r="O46" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="29.25">
+      <c r="P46" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="29.25" hidden="1">
       <c r="A47" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C47" s="1"/>
-      <c r="O47" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="29.25">
+      <c r="P47" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="29.25" hidden="1">
       <c r="A48" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="O48" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="29.25">
+        <v>19</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="P48" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="29.25">
       <c r="A49" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="G49" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P49" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="29.25">
+      <c r="A50" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="O49" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="29.25">
-      <c r="A50" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="B50" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E50" s="3">
         <v>100</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>34</v>
+      <c r="F50" s="12">
+        <v>46174</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="O50" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="43.5">
+        <v>116</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="P50" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="43.5">
       <c r="A51" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E51" s="3">
         <v>100</v>
       </c>
-      <c r="H51" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>111</v>
+      <c r="F51" s="12">
+        <v>46174</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>145</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="O51" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="43.5">
+        <v>116</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P51" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="43.5" hidden="1">
       <c r="A52" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E52" s="3">
         <v>50</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>144</v>
+      <c r="G52" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+        <v>149</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" hidden="1">
       <c r="A53" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="P53" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E54" s="3">
         <v>100</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="K54" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="O54" s="4"/>
-    </row>
-    <row r="55" spans="1:15" ht="29.25">
+        <v>116</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="P54" s="4"/>
+    </row>
+    <row r="55" spans="1:16" ht="29.25">
       <c r="A55" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E55" s="5">
         <v>1</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>111</v>
+        <v>50</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O55" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+        <v>116</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="P55" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" hidden="1">
       <c r="A56" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E56" s="3">
         <v>100</v>
       </c>
-      <c r="O56" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="P56" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" hidden="1">
       <c r="A57" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="P57" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" hidden="1">
       <c r="A58" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+      <c r="P58" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" hidden="1">
       <c r="A59" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="P59" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" hidden="1">
       <c r="A60" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="115.5">
+      <c r="P60" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="115.5">
       <c r="A61" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>111</v>
+      <c r="J61" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="N61" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="O61" s="4"/>
-    </row>
-    <row r="62" spans="1:15" ht="201.75">
+        <v>116</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="P61" s="4"/>
+    </row>
+    <row r="62" spans="1:16" ht="201.75">
       <c r="A62" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E62" s="3">
         <v>70</v>
       </c>
-      <c r="I62" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="O62" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="43.5">
+      <c r="J62" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="P62" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="43.5" hidden="1">
       <c r="A63" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E63" s="3">
         <v>20</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O63" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="87">
+      <c r="G63" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P63" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="87">
       <c r="A64" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E64" s="3">
         <v>60</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="G64" s="3" t="s">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="O64" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="57.75">
+        <v>84</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="P64" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="57.75" hidden="1">
       <c r="A65" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E65" s="3">
         <v>80</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>22</v>
+      <c r="G65" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O65" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" ht="43.5">
+        <v>23</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P65" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="43.5" hidden="1">
       <c r="A66" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="O66" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" ht="57.75">
+        <v>23</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="P66" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="57.75" hidden="1">
       <c r="A67" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E67" s="5">
         <v>0.9</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>24</v>
+      <c r="F67" s="5"/>
+      <c r="G67" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O67" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" ht="57.75">
+        <v>25</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P67" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="57.75" hidden="1">
       <c r="A68" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E68" s="5">
         <v>0.9</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>24</v>
+      <c r="F68" s="5"/>
+      <c r="G68" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="O68" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" ht="57.75">
+        <v>25</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P68" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="57.75" hidden="1">
       <c r="A69" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E69" s="5">
         <v>0.8</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="F69" s="5"/>
       <c r="G69" s="3" t="s">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N69" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O69" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" ht="43.5">
+        <v>25</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P69" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="43.5" hidden="1">
       <c r="A70" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="O70" s="3" t="s">
-        <v>34</v>
+        <v>65</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O70" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}"/>
+  <autoFilter ref="A1:P70" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Caron*"/>
+        <filter val="Dan*"/>
+        <filter val="Jason *"/>
+        <filter val="Jason*"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="I55" r:id="rId1" xr:uid="{5DBA3A74-260E-4C5A-B9BA-696E7347EBA4}"/>
-    <hyperlink ref="I61" r:id="rId2" xr:uid="{2A438ECF-BCA9-41C5-8312-3C3516217E53}"/>
-    <hyperlink ref="I62" r:id="rId3" xr:uid="{58ED2A1A-5B33-45E8-BCEE-062436754878}"/>
+    <hyperlink ref="J55" r:id="rId1" xr:uid="{5DBA3A74-260E-4C5A-B9BA-696E7347EBA4}"/>
+    <hyperlink ref="J61" r:id="rId2" xr:uid="{2A438ECF-BCA9-41C5-8312-3C3516217E53}"/>
+    <hyperlink ref="J62" r:id="rId3" xr:uid="{58ED2A1A-5B33-45E8-BCEE-062436754878}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId4"/>

--- a/KT Compliance.xlsx
+++ b/KT Compliance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://powerschoolgroup-my.sharepoint.com/personal/prabha_parthasarathy_powerschool_com/Documents/GPM/2026/KT 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="605" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F9C925D-D582-43D3-9E0A-C0313C2C8678}"/>
+  <xr:revisionPtr revIDLastSave="697" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0A180E6-26E3-45E0-A5E3-69501D5E9AB4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B7FEA37-02A6-41FF-9931-0A86E2A764FA}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="185">
   <si>
     <t>Product Area</t>
   </si>
@@ -141,37 +141,34 @@
     <t>MA</t>
   </si>
   <si>
-    <t>chhaya</t>
-  </si>
-  <si>
-    <t>Turab</t>
+    <t>Chhaya</t>
+  </si>
+  <si>
+    <t>Turab/NewHire</t>
+  </si>
+  <si>
+    <t>USKT</t>
+  </si>
+  <si>
+    <t>SIF Unity parallel coming up.</t>
+  </si>
+  <si>
+    <t>SIF Unity tickets created.</t>
+  </si>
+  <si>
+    <t>MI Ed-Fi</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
   <si>
     <t>Not Required</t>
   </si>
   <si>
-    <t>Sif Unity parellal coming up.</t>
-  </si>
-  <si>
-    <t>Sif Unity tickets created.</t>
-  </si>
-  <si>
-    <t>MI Ed-fi</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>ShanNita*</t>
-  </si>
-  <si>
-    <t>Not required</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>MN ed-fi</t>
+    <t>MN Ed-Fi</t>
   </si>
   <si>
     <t>BC</t>
@@ -231,7 +228,7 @@
     <t>ShanNita</t>
   </si>
   <si>
-    <t>WI Ed-fi</t>
+    <t>WI Ed-Fi</t>
   </si>
   <si>
     <t>WY</t>
@@ -277,7 +274,7 @@
     <t>Jessica and Turab are involved in the state from the beginning. KT not required.</t>
   </si>
   <si>
-    <t>CEDs</t>
+    <t>CEDS</t>
   </si>
   <si>
     <t>Soumya</t>
@@ -301,7 +298,7 @@
     <t>NM</t>
   </si>
   <si>
-    <t xml:space="preserve">Eric </t>
+    <t>Eric -&gt;Michael</t>
   </si>
   <si>
     <t xml:space="preserve">Eric -&gt; Micheal  </t>
@@ -313,16 +310,19 @@
     <t xml:space="preserve">Anuj </t>
   </si>
   <si>
-    <t>jessica/ Turab</t>
-  </si>
-  <si>
     <t>VT</t>
   </si>
   <si>
     <t>Ajish</t>
   </si>
   <si>
-    <t>Vette</t>
+    <t>Vette/Newhire</t>
+  </si>
+  <si>
+    <t>Not started</t>
+  </si>
+  <si>
+    <t>Not required</t>
   </si>
   <si>
     <t>Vette leads all meetings</t>
@@ -334,10 +334,7 @@
     <t>ID</t>
   </si>
   <si>
-    <t>Michael/ Debra</t>
-  </si>
-  <si>
-    <t>Not started</t>
+    <t>Michael</t>
   </si>
   <si>
     <t>All</t>
@@ -349,7 +346,7 @@
     <t>UDC</t>
   </si>
   <si>
-    <t>TX</t>
+    <t>TX(esp)</t>
   </si>
   <si>
     <t>Rajesh (eSP)</t>
@@ -370,6 +367,9 @@
     <t>MS</t>
   </si>
   <si>
+    <t>Jessica/Caron*</t>
+  </si>
+  <si>
     <t>ON</t>
   </si>
   <si>
@@ -391,9 +391,15 @@
     <t>Ankit</t>
   </si>
   <si>
+    <t>Fred/Newhire</t>
+  </si>
+  <si>
     <t>Sif Unity, IA current backlog and future commitments</t>
   </si>
   <si>
+    <t>Sif Unity yearcoming up.</t>
+  </si>
+  <si>
     <t>Fred is involved in all calls</t>
   </si>
   <si>
@@ -406,9 +412,6 @@
     <t>MT</t>
   </si>
   <si>
-    <t>Turab/ Jessica</t>
-  </si>
-  <si>
     <t>Chintan is handling this independently</t>
   </si>
   <si>
@@ -421,7 +424,10 @@
     <t>NY</t>
   </si>
   <si>
-    <t>CA</t>
+    <t>Shereen/NewHire</t>
+  </si>
+  <si>
+    <t>CA(esp)</t>
   </si>
   <si>
     <t>Rohan (eSP)</t>
@@ -451,18 +457,30 @@
     <t>Debra</t>
   </si>
   <si>
-    <t>in process</t>
+    <t>MD(esp)</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>From June</t>
+  </si>
+  <si>
+    <t>NJ(esp)</t>
   </si>
   <si>
     <t>Prashu gave this to Rajesh few months back and its now coming back</t>
   </si>
   <si>
-    <t>18th May is the Sync up Call. No open items and ongoing discussion. KT is not required</t>
-  </si>
-  <si>
     <t>No KT required, Prashu is already taking care of this</t>
   </si>
   <si>
+    <t>Prashu is handling from March</t>
+  </si>
+  <si>
     <t>Rohan</t>
   </si>
   <si>
@@ -470,49 +488,49 @@
   </si>
   <si>
     <t>Prashu Already handling OR state since Feb 2026</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Fred is involved in the state from the beginning. KT not required. We have a sync up call on 18th May to discuss any ongoing open items</t>
   </si>
   <si>
     <t xml:space="preserve">CRDC
 </t>
   </si>
   <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>Jessica?</t>
-  </si>
-  <si>
-    <t>REquired</t>
-  </si>
-  <si>
-    <t>Not Required (GONE)</t>
-  </si>
-  <si>
-    <t>OH</t>
+    <t>IL(esp)</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>MA(esp)</t>
+  </si>
+  <si>
+    <t>Not Applicable (GONE)</t>
+  </si>
+  <si>
+    <t>OH(esp)</t>
+  </si>
+  <si>
+    <t>VA(esp)</t>
+  </si>
+  <si>
+    <t>WA(esp)</t>
+  </si>
+  <si>
+    <t>Only till June 26</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>Sivaprasad</t>
+  </si>
+  <si>
+    <t>Caron*</t>
+  </si>
+  <si>
+    <t>Everything</t>
   </si>
   <si>
     <t>WA</t>
-  </si>
-  <si>
-    <t>Only till June 26</t>
-  </si>
-  <si>
-    <t>LA</t>
-  </si>
-  <si>
-    <t>Sivaprasad</t>
-  </si>
-  <si>
-    <t>Caron*</t>
-  </si>
-  <si>
-    <t>Everything</t>
   </si>
   <si>
     <t>Dan*</t>
@@ -543,6 +561,9 @@
     <t>N/A</t>
   </si>
   <si>
+    <t>IL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prashu </t>
   </si>
   <si>
@@ -558,6 +579,9 @@
     <t>NH</t>
   </si>
   <si>
+    <t>OH</t>
+  </si>
+  <si>
     <t>Meta</t>
   </si>
   <si>
@@ -582,6 +606,12 @@
     <t>NE</t>
   </si>
   <si>
+    <t>Turab/ Caron*</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
     <t>Day  to Day Backlog management and sprint planning. Customer Introduction</t>
   </si>
   <si>
@@ -603,7 +633,13 @@
     <t>SC</t>
   </si>
   <si>
+    <t>Vette</t>
+  </si>
+  <si>
     <t>TN</t>
+  </si>
+  <si>
+    <t>TX</t>
   </si>
   <si>
     <t>26-27 Requirements</t>
@@ -1087,11 +1123,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P70"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="3" width="8.85546875" style="3"/>
+    <col min="1" max="1" width="10.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="19" style="11" customWidth="1"/>
     <col min="5" max="6" width="10.5703125" style="3" customWidth="1"/>
     <col min="7" max="7" width="17" style="3" customWidth="1"/>
@@ -1106,7 +1143,7 @@
     <col min="17" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="8" customFormat="1" ht="144.75">
+    <row r="1" spans="1:16" s="8" customFormat="1" ht="129.6">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1156,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1">
+    <row r="2" spans="1:16" ht="28.9">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -1182,7 +1219,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="29.25" hidden="1">
+    <row r="3" spans="1:16" ht="28.9">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -1190,33 +1227,33 @@
         <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="28.9">
+      <c r="A4" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="P3" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="29.25" hidden="1">
-      <c r="A4" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -1225,18 +1262,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1">
+    <row r="5" spans="1:16">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -1245,79 +1282,79 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="57.75" hidden="1">
+    <row r="6" spans="1:16" ht="57.6">
       <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="D6" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="P6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:16" ht="28.9">
+      <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="29.25">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="11" t="s">
         <v>38</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>39</v>
       </c>
       <c r="E7" s="3">
         <v>90</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="P7" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" hidden="1">
-      <c r="A8" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -1326,32 +1363,32 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1">
+    <row r="9" spans="1:16">
       <c r="A9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="28.9">
+      <c r="A10" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="P9" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="29.25" hidden="1">
-      <c r="A10" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>19</v>
@@ -1363,15 +1400,15 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="29.25">
+    <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>23</v>
@@ -1380,45 +1417,45 @@
         <v>100</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="K11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11" s="3" t="s">
+      <c r="P11" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="43.15">
+      <c r="A12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="P11" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="57.75" hidden="1">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="D12" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E12" s="3">
         <v>90</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>23</v>
@@ -1433,67 +1470,67 @@
         <v>23</v>
       </c>
       <c r="O12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P12" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="57.6">
+      <c r="A13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="P12" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="57.75" hidden="1">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="D13" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E13" s="3">
         <v>100</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P13" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1">
+    <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="P14" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" hidden="1">
-      <c r="A15" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1502,49 +1539,49 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="29.25" hidden="1">
+    <row r="16" spans="1:16" ht="28.9">
       <c r="A16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" hidden="1">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="P17" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="28.9">
+      <c r="A18" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="P17" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" hidden="1">
-      <c r="A18" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>19</v>
@@ -1553,21 +1590,21 @@
         <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P18" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="57.6">
+      <c r="A19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="P18" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="57.75" hidden="1">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>19</v>
@@ -1576,46 +1613,46 @@
         <v>100</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P19" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="57.75" hidden="1">
+    <row r="20" spans="1:16" ht="43.15">
       <c r="A20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="D20" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>19</v>
       </c>
       <c r="E20" s="5">
         <v>0.9</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>78</v>
@@ -1624,178 +1661,178 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="21" spans="1:16" hidden="1">
+    <row r="21" spans="1:16">
       <c r="A21" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D21" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P21" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="29.25" hidden="1">
+    <row r="22" spans="1:16">
       <c r="A22" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" hidden="1">
-      <c r="A23" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="159" hidden="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="144">
       <c r="A24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D24" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" s="3">
         <v>90</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P24" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="29.25" hidden="1">
+    <row r="25" spans="1:16" ht="28.9">
       <c r="A25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="K25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="57.6">
+      <c r="A26" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="57.75" hidden="1">
-      <c r="A26" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="D26" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E26" s="3">
         <v>100</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P26" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1">
+    <row r="27" spans="1:16">
       <c r="A27" s="2" t="s">
         <v>93</v>
       </c>
@@ -1803,10 +1840,10 @@
         <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E27" s="3">
         <v>100</v>
@@ -1815,7 +1852,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1">
+    <row r="28" spans="1:16">
       <c r="A28" s="2" t="s">
         <v>94</v>
       </c>
@@ -1826,7 +1863,7 @@
         <v>95</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E28" s="3">
         <v>100</v>
@@ -1835,7 +1872,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1">
+    <row r="29" spans="1:16">
       <c r="A29" s="2" t="s">
         <v>96</v>
       </c>
@@ -1846,7 +1883,7 @@
         <v>95</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E29" s="3">
         <v>100</v>
@@ -1855,24 +1892,24 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1">
+    <row r="30" spans="1:16">
       <c r="A30" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D30" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P30" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="43.5" hidden="1">
+    <row r="31" spans="1:16" ht="43.15">
       <c r="A31" s="2" t="s">
         <v>98</v>
       </c>
@@ -1880,181 +1917,183 @@
         <v>99</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="E31" s="5">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P31" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="29.25" hidden="1">
+    <row r="32" spans="1:16" ht="28.9">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="O32" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="P32" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="43.5" hidden="1">
+    <row r="33" spans="1:16" ht="28.9">
       <c r="A33" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E33" s="3">
         <v>20</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P33" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="29.25" hidden="1">
+    <row r="34" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="P34" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="29.25" hidden="1">
+    <row r="35" spans="1:16" ht="28.9">
       <c r="A35" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" s="2"/>
+      <c r="C35" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="D35" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="P35" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="57.75" hidden="1">
+    <row r="36" spans="1:16" ht="57.6">
       <c r="A36" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E36" s="3">
         <v>100</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P36" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="29.25" hidden="1">
+    <row r="37" spans="1:16">
       <c r="A37" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E37" s="3">
         <v>0</v>
@@ -2063,169 +2102,205 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="57.75" hidden="1">
+    <row r="38" spans="1:16">
       <c r="A38" s="2" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E38" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="P38" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="57.75" hidden="1">
+    <row r="39" spans="1:16" ht="57.6">
       <c r="A39" s="2" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E39" s="3">
         <v>100</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="P39" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="57.75" hidden="1">
+    <row r="40" spans="1:16" ht="57.6">
       <c r="A40" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E40" s="3">
         <v>100</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="P40" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="43.15">
+      <c r="A41" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="P40" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="43.5" hidden="1">
-      <c r="A41" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="D41" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E41" s="3">
         <v>100</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="P41" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="87" hidden="1">
+    <row r="42" spans="1:16">
       <c r="A42" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="D42" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E42" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="P42" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="29.25" hidden="1">
+    <row r="43" spans="1:16" ht="28.9">
       <c r="A43" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C43" s="1"/>
       <c r="P43" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="29.25" hidden="1">
+    <row r="44" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="E44" s="3">
         <v>100</v>
@@ -2234,119 +2309,119 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="29.25" hidden="1">
+    <row r="45" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="P45" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="29.25" hidden="1">
+    <row r="46" spans="1:16">
       <c r="A46" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C46" s="1"/>
       <c r="P46" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="29.25" hidden="1">
+    <row r="47" spans="1:16">
       <c r="A47" s="1" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C47" s="1"/>
       <c r="P47" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="29.25" hidden="1">
+    <row r="48" spans="1:16">
       <c r="A48" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="P48" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="29.25">
+    <row r="49" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P49" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="29.25">
+    <row r="50" spans="1:16">
       <c r="A50" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E50" s="3">
         <v>100</v>
@@ -2355,42 +2430,42 @@
         <v>46174</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="P50" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="43.5">
+    <row r="51" spans="1:16" ht="43.15">
       <c r="A51" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E51" s="3">
         <v>100</v>
@@ -2399,144 +2474,144 @@
         <v>46174</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P51" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="43.5" hidden="1">
+    <row r="52" spans="1:16" ht="43.15">
       <c r="A52" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="D52" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E52" s="3">
         <v>50</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" hidden="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53" s="2" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="D53" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E53" s="3">
         <v>0</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E54" s="3">
         <v>100</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="P54" s="4"/>
     </row>
-    <row r="55" spans="1:16" ht="29.25">
+    <row r="55" spans="1:16">
       <c r="A55" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E55" s="5">
         <v>1</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P55" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1">
+    <row r="56" spans="1:16">
       <c r="A56" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>23</v>
@@ -2545,7 +2620,7 @@
         <v>95</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E56" s="3">
         <v>100</v>
@@ -2554,9 +2629,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1">
+    <row r="57" spans="1:16">
       <c r="A57" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>23</v>
@@ -2565,7 +2640,7 @@
         <v>95</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
@@ -2574,18 +2649,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="58" spans="1:16" hidden="1">
+    <row r="58" spans="1:16">
       <c r="A58" s="2" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
@@ -2594,9 +2669,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1">
+    <row r="59" spans="1:16">
       <c r="A59" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>23</v>
@@ -2605,7 +2680,7 @@
         <v>95</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E59" s="3">
         <v>100</v>
@@ -2614,9 +2689,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1">
+    <row r="60" spans="1:16">
       <c r="A60" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>23</v>
@@ -2625,7 +2700,7 @@
         <v>95</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E60" s="3">
         <v>100</v>
@@ -2634,147 +2709,147 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="115.5">
+    <row r="61" spans="1:16" ht="86.45">
       <c r="A61" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="P61" s="4"/>
     </row>
-    <row r="62" spans="1:16" ht="201.75">
+    <row r="62" spans="1:16" ht="144">
       <c r="A62" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E62" s="3">
         <v>70</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P62" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="43.5" hidden="1">
+    <row r="63" spans="1:16" ht="28.9">
       <c r="A63" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E63" s="3">
         <v>20</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P63" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="87">
+    <row r="64" spans="1:16" ht="72">
       <c r="A64" s="2" t="s">
-        <v>110</v>
+        <v>172</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E64" s="3">
         <v>60</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="P64" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="57.75" hidden="1">
+    <row r="65" spans="1:16" ht="43.15">
       <c r="A65" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E65" s="3">
         <v>80</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>23</v>
@@ -2786,60 +2861,60 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="43.5" hidden="1">
+    <row r="66" spans="1:16" ht="43.15">
       <c r="A66" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="P66" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="57.75" hidden="1">
+    <row r="67" spans="1:16" ht="43.15">
       <c r="A67" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E67" s="5">
         <v>0.9</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>78</v>
@@ -2848,37 +2923,37 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="57.75" hidden="1">
+    <row r="68" spans="1:16" ht="43.15">
       <c r="A68" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E68" s="5">
         <v>0.9</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>78</v>
@@ -2887,76 +2962,67 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="57.75" hidden="1">
+    <row r="69" spans="1:16" ht="43.15">
       <c r="A69" s="2" t="s">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E69" s="5">
         <v>0.8</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P69" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="43.5" hidden="1">
+    <row r="70" spans="1:16" ht="28.9">
       <c r="A70" s="2" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="D70" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D70" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="P70" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P70" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Caron*"/>
-        <filter val="Dan*"/>
-        <filter val="Jason *"/>
-        <filter val="Jason*"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:P70" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}"/>
   <hyperlinks>
     <hyperlink ref="J55" r:id="rId1" xr:uid="{5DBA3A74-260E-4C5A-B9BA-696E7347EBA4}"/>
     <hyperlink ref="J61" r:id="rId2" xr:uid="{2A438ECF-BCA9-41C5-8312-3C3516217E53}"/>
@@ -2965,4 +3031,394 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId4"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020CF8294E4C5A44CB8AF60CE499E006F" ma:contentTypeVersion="32" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="009ade30d862eccbd4a375ee527febd2">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="5624914c-2aad-4993-a320-2eb67911e80a" xmlns:ns3="41fb0f91-a3b9-4963-8e6c-81696287e595" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a2a584ab283d97548660d8e8b35cff3" ns1:_="" ns2:_="" ns3:_="">
+    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
+    <xsd:import namespace="5624914c-2aad-4993-a320-2eb67911e80a"/>
+    <xsd:import namespace="41fb0f91-a3b9-4963-8e6c-81696287e595"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:_Flow_SignoffStatus" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:Comments" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:JiraTicket" minOccurs="0"/>
+                <xsd:element ref="ns3:Demodate" minOccurs="0"/>
+                <xsd:element ref="ns3:Demogivenby" minOccurs="0"/>
+                <xsd:element ref="ns3:DemoBy" minOccurs="0"/>
+                <xsd:element ref="ns3:Demodated" minOccurs="0"/>
+                <xsd:element ref="ns3:ZoomPassword" minOccurs="0"/>
+                <xsd:element ref="ns3:TicketNumbers" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:Comments0" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="20" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5624914c-2aad-4993-a320-2eb67911e80a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="33" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{1e3d70b8-4039-4492-b181-b14aed0b7cfc}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="5624914c-2aad-4993-a320-2eb67911e80a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="41fb0f91-a3b9-4963-8e6c-81696287e595" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_Flow_SignoffStatus" ma:index="15" nillable="true" ma:displayName="Jira Ticket" ma:internalName="_x0024_Resources_x003a_core_x002c_Signoff_Status_x003b_">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Comments" ma:index="18" nillable="true" ma:displayName="Issue description" ma:format="Dropdown" ma:internalName="Comments">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="21" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="22" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="JiraTicket" ma:index="23" nillable="true" ma:displayName="Jira Ticket" ma:format="Dropdown" ma:internalName="JiraTicket">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Demodate" ma:index="24" nillable="true" ma:displayName="Demo date" ma:format="DateOnly" ma:internalName="Demodate">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Demogivenby" ma:index="25" nillable="true" ma:displayName="Demo given by" ma:format="Dropdown" ma:internalName="Demogivenby">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="DemoBy" ma:index="26" nillable="true" ma:displayName="Demo By" ma:format="Dropdown" ma:internalName="DemoBy">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Demodated" ma:index="27" nillable="true" ma:displayName="Demo dated" ma:format="DateOnly" ma:internalName="Demodated">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ZoomPassword" ma:index="28" nillable="true" ma:displayName="Zoom Password" ma:format="Dropdown" ma:internalName="ZoomPassword">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TicketNumbers" ma:index="29" nillable="true" ma:displayName="Ticket Numbers" ma:format="Dropdown" ma:internalName="TicketNumbers">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="30" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="32" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="446d0db8-b9c6-471a-b6ad-ff86e727147a" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="34" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="35" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Comments0" ma:index="36" nillable="true" ma:displayName="Comments" ma:format="Dropdown" ma:internalName="Comments0">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="37" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Demogivenby xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <DemoBy xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Comments0 xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <TaxCatchAll xmlns="5624914c-2aad-4993-a320-2eb67911e80a" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <ZoomPassword xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Demodate xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <JiraTicket xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Comments xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <TicketNumbers xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Demodated xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DABEB6D-3BAD-47AB-9B08-E3D505D0C37F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{062249BE-4AA3-4403-8E45-C85EF69B7519}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF7AA70-C622-4509-9661-E5AB3E79D417}"/>
 </file>
--- a/KT Compliance.xlsx
+++ b/KT Compliance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://powerschoolgroup-my.sharepoint.com/personal/prabha_parthasarathy_powerschool_com/Documents/GPM/2026/KT 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="697" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0A180E6-26E3-45E0-A5E3-69501D5E9AB4}"/>
+  <xr:revisionPtr revIDLastSave="765" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D431BA88-1CB3-43A1-9A77-660242CF9A38}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B7FEA37-02A6-41FF-9931-0A86E2A764FA}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$P$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$P$69</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -57,7 +57,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="A45" authorId="1" shapeId="0" xr:uid="{2444CFCC-5DB3-4AD6-AA9D-9D23ACFB4185}">
+    <comment ref="A44" authorId="1" shapeId="0" xr:uid="{2444CFCC-5DB3-4AD6-AA9D-9D23ACFB4185}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="193">
   <si>
     <t>Product Area</t>
   </si>
@@ -153,9 +153,6 @@
     <t>SIF Unity parallel coming up.</t>
   </si>
   <si>
-    <t>SIF Unity tickets created.</t>
-  </si>
-  <si>
     <t>MI Ed-Fi</t>
   </si>
   <si>
@@ -412,9 +409,6 @@
     <t>MT</t>
   </si>
   <si>
-    <t>Chintan is handling this independently</t>
-  </si>
-  <si>
     <t>FL (esp )</t>
   </si>
   <si>
@@ -449,9 +443,6 @@
   </si>
   <si>
     <t>Prashu will lead customer calls from June</t>
-  </si>
-  <si>
-    <t>FL</t>
   </si>
   <si>
     <t>Debra</t>
@@ -618,9 +609,6 @@
     <t>CA Transition Document</t>
   </si>
   <si>
-    <t>Not Done yet</t>
-  </si>
-  <si>
     <t>AL</t>
   </si>
   <si>
@@ -647,13 +635,50 @@
   <si>
     <t xml:space="preserve">Ed-fi, DEX
 </t>
+  </si>
+  <si>
+    <t>Micheal will start from Q3/Q4</t>
+  </si>
+  <si>
+    <t>KT not started</t>
+  </si>
+  <si>
+    <t>Jason leading calls</t>
+  </si>
+  <si>
+    <t>Not planned</t>
+  </si>
+  <si>
+    <t>Ticket handling with India team by Alka</t>
+  </si>
+  <si>
+    <t>Shannita handles all customer intercations</t>
+  </si>
+  <si>
+    <t>Dan handles all customer intercations</t>
+  </si>
+  <si>
+    <t>Caron will start running the calls from Aug.</t>
+  </si>
+  <si>
+    <t>No plan</t>
+  </si>
+  <si>
+    <t>SIF Unity tickets created.
+Chhaya is part of all calls with customer and handling tickets.</t>
+  </si>
+  <si>
+    <t>July - Micheal is yet to start customer calls or ticket handling</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -692,7 +717,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -702,6 +727,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,7 +765,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -768,6 +799,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1115,7 +1155,7 @@
     <text xml:space="preserve">Last year of support
 </text>
   </threadedComment>
-  <threadedComment ref="A45" dT="2024-12-05T16:50:38.65" personId="{D3206E26-97D1-4EED-9A9C-AC1B96B26E03}" id="{2444CFCC-5DB3-4AD6-AA9D-9D23ACFB4185}">
+  <threadedComment ref="A44" dT="2024-12-05T16:50:38.65" personId="{D3206E26-97D1-4EED-9A9C-AC1B96B26E03}" id="{2444CFCC-5DB3-4AD6-AA9D-9D23ACFB4185}">
     <text>Last year of support</text>
   </threadedComment>
 </ThreadedComments>
@@ -1123,27 +1163,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
-  <dimension ref="A1:P70"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:P69"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="19" style="11" customWidth="1"/>
-    <col min="5" max="6" width="10.5703125" style="3" customWidth="1"/>
+    <col min="5" max="6" width="10.5546875" style="3" customWidth="1"/>
     <col min="7" max="7" width="17" style="3" customWidth="1"/>
     <col min="8" max="8" width="25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.88671875" style="3" customWidth="1"/>
     <col min="10" max="10" width="15" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.140625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.85546875" style="3"/>
-    <col min="15" max="15" width="28.28515625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="16.140625" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="8.85546875" style="3"/>
+    <col min="11" max="11" width="16.109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.88671875" style="3"/>
+    <col min="15" max="15" width="28.33203125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16.109375" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="8" customFormat="1" ht="129.6">
+    <row r="1" spans="1:16" s="8" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1193,7 +1234,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="28.9">
+    <row r="2" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -1213,41 +1254,41 @@
         <v>20</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P2" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="28.9">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3">
+        <v>100</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3">
-        <v>100</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="P3" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="28.9">
-      <c r="A4" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
@@ -1262,130 +1303,142 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="3">
+        <v>100</v>
+      </c>
+      <c r="P5" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="3">
-        <v>100</v>
-      </c>
-      <c r="P5" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="57.6">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D6" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="28.9">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="3">
-        <v>90</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P7" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="P8" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="3">
-        <v>100</v>
-      </c>
-      <c r="P8" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="3">
+        <v>80</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="28.9">
-      <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>18</v>
@@ -1400,188 +1453,197 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="3">
+        <v>100</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="11" t="s">
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P11" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="E11" s="3">
-        <v>100</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P11" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="43.15">
-      <c r="A12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="E12" s="3">
         <v>90</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="P12" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P12" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="57.6">
-      <c r="A13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="3">
+        <v>100</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="3">
-        <v>100</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="P13" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="P14" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="P15" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="3">
-        <v>100</v>
-      </c>
-      <c r="P15" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="28.9">
-      <c r="A16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="2" t="s">
+      <c r="E17" s="3">
+        <v>80</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="P17" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="P17" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="28.9">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>19</v>
@@ -1590,18 +1652,18 @@
         <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P18" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="P18" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="57.6">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>18</v>
@@ -1613,815 +1675,869 @@
         <v>100</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P19" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="43.15">
+    <row r="20" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="E20" s="5">
         <v>0.9</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O20" s="3" t="s">
+      <c r="P20" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="P20" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="2" t="s">
+      <c r="B21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="3">
+        <v>80</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="P21" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="P21" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="2" t="s">
+      <c r="B22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="3">
+        <v>20</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="144" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="B24" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="144">
-      <c r="A24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="3">
-        <v>90</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="P24" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="28.9">
+    <row r="25" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="3">
+        <v>100</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="K25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="57.6">
-      <c r="A26" s="2" t="s">
+      <c r="B26" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="D26" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" s="3">
         <v>100</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P26" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="3">
+        <v>100</v>
+      </c>
+      <c r="P27" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="3">
-        <v>100</v>
-      </c>
-      <c r="P27" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="A28" s="2" t="s">
+      <c r="E28" s="3">
+        <v>100</v>
+      </c>
+      <c r="P28" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="D29" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="3">
-        <v>100</v>
-      </c>
-      <c r="P28" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="A29" s="2" t="s">
+      <c r="E29" s="3">
+        <v>100</v>
+      </c>
+      <c r="P29" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3">
-        <v>100</v>
-      </c>
-      <c r="P29" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="A30" s="2" t="s">
+      <c r="E30" s="3">
+        <v>80</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="P30" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="P30" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="43.15">
-      <c r="A31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="D31" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31" s="5">
         <v>0.7</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="I31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O31" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O31" s="3" t="s">
+      <c r="P31" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P31" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="28.9">
-      <c r="A32" s="2" t="s">
+      <c r="B32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H32" s="3" t="s">
+      <c r="I32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P32" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="P32" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="28.9">
-      <c r="A33" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E33" s="3">
         <v>20</v>
       </c>
       <c r="G33" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="P33" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="P33" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="A34" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
       </c>
       <c r="P34" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="28.9">
+    <row r="35" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P35" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="P35" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="57.6">
-      <c r="A36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="D36" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="3">
+        <v>100</v>
+      </c>
+      <c r="G36" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="I36" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E36" s="3">
-        <v>100</v>
-      </c>
-      <c r="G36" s="3" t="s">
+      <c r="K36" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="L36" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O36" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O36" s="3" t="s">
+      <c r="P36" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="P36" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="2" t="s">
+      <c r="B37" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" s="3">
+        <v>100</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="I37" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" s="3">
-        <v>0</v>
+      <c r="K37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="P37" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16">
-      <c r="A38" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B38" s="1" t="s">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="3">
+        <v>100</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="P38" s="4">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E39" s="3">
+        <v>100</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P39" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E40" s="3">
+        <v>100</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="P40" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E38" s="3">
-        <v>100</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K38" s="3" t="s">
+      <c r="D41" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="P38" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="57.6">
-      <c r="A39" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E39" s="3">
-        <v>100</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="P39" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="57.6">
-      <c r="A40" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B40" s="1" t="s">
+      <c r="E41" s="3">
+        <v>100</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P41" s="4">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" s="3">
-        <v>100</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="P40" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="43.15">
-      <c r="A41" s="2" t="s">
+      <c r="B42" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="P42" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E41" s="3">
-        <v>100</v>
-      </c>
-      <c r="G41" s="3" t="s">
+      <c r="B43" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="P41" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16">
-      <c r="A42" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="3">
-        <v>100</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="P42" s="4">
-        <v>46206</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="28.9">
-      <c r="A43" s="2" t="s">
+      <c r="D43" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="P43" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C43" s="1"/>
-      <c r="P43" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="A44" s="2" t="s">
+      <c r="B44" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C44" s="1" t="s">
+      <c r="P44" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D44" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E44" s="3">
-        <v>100</v>
-      </c>
-      <c r="P44" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="A45" s="2" t="s">
+      <c r="B45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="P45" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="P45" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="B46" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C46" s="1"/>
       <c r="P46" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P47" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C47" s="1"/>
-      <c r="P47" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="A48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C48" s="1"/>
+      <c r="C48" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="D48" s="11" t="s">
-        <v>24</v>
+        <v>75</v>
+      </c>
+      <c r="E48" s="3">
+        <v>50</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="P48" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>144</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F49" s="12">
+        <v>46174</v>
       </c>
       <c r="G49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O49" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="P49" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E50" s="3">
         <v>100</v>
@@ -2430,603 +2546,574 @@
         <v>46174</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="P50" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="43.15">
+    <row r="51" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="3">
+        <v>100</v>
+      </c>
+      <c r="G51" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E51" s="3">
-        <v>100</v>
-      </c>
-      <c r="F51" s="12">
-        <v>46174</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>151</v>
       </c>
+      <c r="J51" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="K51" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P51" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="43.15">
+        <v>152</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" s="3">
+        <v>100</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="P53" s="4"/>
+    </row>
+    <row r="54" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" s="15">
+        <v>100</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="P54" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="15">
+        <v>100</v>
+      </c>
+      <c r="P55" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="15">
+        <v>100</v>
+      </c>
+      <c r="P56" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="15">
+        <v>100</v>
+      </c>
+      <c r="P57" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" s="15">
+        <v>100</v>
+      </c>
+      <c r="P58" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="15">
+        <v>100</v>
+      </c>
+      <c r="P59" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E60" s="15">
+        <v>100</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="P60" s="4"/>
+    </row>
+    <row r="61" spans="1:16" ht="144" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="P61" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E62" s="3">
+        <v>20</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="P62" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E63" s="3">
+        <v>100</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I63" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" s="3">
-        <v>50</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16">
-      <c r="A53" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" s="3">
-        <v>0</v>
-      </c>
-      <c r="P53" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16">
-      <c r="A54" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E54" s="3">
-        <v>100</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="P54" s="4"/>
-    </row>
-    <row r="55" spans="1:16">
-      <c r="A55" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E55" s="5">
-        <v>1</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="P55" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16">
-      <c r="A56" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="3">
-        <v>100</v>
-      </c>
-      <c r="P56" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16">
-      <c r="A57" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="3">
-        <v>100</v>
-      </c>
-      <c r="P57" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16">
-      <c r="A58" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="3">
-        <v>100</v>
-      </c>
-      <c r="P58" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16">
-      <c r="A59" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="3">
-        <v>100</v>
-      </c>
-      <c r="P59" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16">
-      <c r="A60" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="3">
-        <v>100</v>
-      </c>
-      <c r="P60" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" ht="86.45">
-      <c r="A61" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E61" s="3">
-        <v>100</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="O61" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="P61" s="4"/>
-    </row>
-    <row r="62" spans="1:16" ht="144">
-      <c r="A62" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E62" s="3">
-        <v>70</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="P62" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" ht="28.9">
-      <c r="A63" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="J63" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D63" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E63" s="3">
-        <v>20</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>107</v>
+      <c r="K63" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="P63" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="72">
+    <row r="64" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="E64" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G64" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P64" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="H64" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J64" s="3" t="s">
+      <c r="B65" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="K64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N64" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="O64" s="3" t="s">
+      <c r="P65" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="P64" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" ht="43.15">
-      <c r="A65" s="2" t="s">
+      <c r="B66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" s="3">
-        <v>80</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K65" s="3" t="s">
+      <c r="D66" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L65" s="3" t="s">
+      <c r="E66" s="3">
+        <v>90</v>
+      </c>
+      <c r="F66" s="5"/>
+      <c r="G66" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P66" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D67" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="P65" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" ht="43.15">
-      <c r="A66" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="P66" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="43.15">
-      <c r="A67" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="5">
-        <v>0.9</v>
+      <c r="E67" s="3">
+        <v>90</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I67" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O67" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J67" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="P67" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="43.15">
+    <row r="68" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>180</v>
+        <v>86</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="5">
-        <v>0.9</v>
+        <v>23</v>
+      </c>
+      <c r="E68" s="3">
+        <v>80</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="P68" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="43.15">
+    <row r="69" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E69" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="F69" s="5"/>
-      <c r="G69" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O69" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="P69" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="28.9">
-      <c r="A70" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C70" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D70" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="P70" s="3" t="s">
-        <v>34</v>
+      <c r="P69" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P70" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}"/>
+  <autoFilter ref="A1:P69" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Soumya"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="J55" r:id="rId1" xr:uid="{5DBA3A74-260E-4C5A-B9BA-696E7347EBA4}"/>
-    <hyperlink ref="J61" r:id="rId2" xr:uid="{2A438ECF-BCA9-41C5-8312-3C3516217E53}"/>
-    <hyperlink ref="J62" r:id="rId3" xr:uid="{58ED2A1A-5B33-45E8-BCEE-062436754878}"/>
+    <hyperlink ref="J54" r:id="rId1" xr:uid="{5DBA3A74-260E-4C5A-B9BA-696E7347EBA4}"/>
+    <hyperlink ref="J60" r:id="rId2" xr:uid="{2A438ECF-BCA9-41C5-8312-3C3516217E53}"/>
+    <hyperlink ref="J61" r:id="rId3" xr:uid="{58ED2A1A-5B33-45E8-BCEE-062436754878}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId4"/>
@@ -3043,6 +3130,29 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Demogivenby xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <DemoBy xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Comments0 xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <TaxCatchAll xmlns="5624914c-2aad-4993-a320-2eb67911e80a" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <ZoomPassword xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Demodate xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <JiraTicket xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Comments xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <TicketNumbers xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Demodated xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020CF8294E4C5A44CB8AF60CE499E006F" ma:contentTypeVersion="32" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="009ade30d862eccbd4a375ee527febd2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="5624914c-2aad-4993-a320-2eb67911e80a" xmlns:ns3="41fb0f91-a3b9-4963-8e6c-81696287e595" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a2a584ab283d97548660d8e8b35cff3" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3388,37 +3498,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Demogivenby xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <DemoBy xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <Comments0 xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <TaxCatchAll xmlns="5624914c-2aad-4993-a320-2eb67911e80a" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <ZoomPassword xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Demodate xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <JiraTicket xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <Comments xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <TicketNumbers xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <Demodated xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DABEB6D-3BAD-47AB-9B08-E3D505D0C37F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DABEB6D-3BAD-47AB-9B08-E3D505D0C37F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{062249BE-4AA3-4403-8E45-C85EF69B7519}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF7AA70-C622-4509-9661-E5AB3E79D417}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="41fb0f91-a3b9-4963-8e6c-81696287e595"/>
+    <ds:schemaRef ds:uri="5624914c-2aad-4993-a320-2eb67911e80a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF7AA70-C622-4509-9661-E5AB3E79D417}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{062249BE-4AA3-4403-8E45-C85EF69B7519}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="5624914c-2aad-4993-a320-2eb67911e80a"/>
+    <ds:schemaRef ds:uri="41fb0f91-a3b9-4963-8e6c-81696287e595"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/KT Compliance.xlsx
+++ b/KT Compliance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://powerschoolgroup-my.sharepoint.com/personal/prabha_parthasarathy_powerschool_com/Documents/GPM/2026/KT 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="765" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D431BA88-1CB3-43A1-9A77-660242CF9A38}"/>
+  <xr:revisionPtr revIDLastSave="817" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D668E19F-7167-4A4F-9CFF-B80BE7F54FDD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B7FEA37-02A6-41FF-9931-0A86E2A764FA}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="192">
   <si>
     <t>Product Area</t>
   </si>
@@ -470,9 +470,6 @@
   </si>
   <si>
     <t>Prashu is handling from March</t>
-  </si>
-  <si>
-    <t>Rohan</t>
   </si>
   <si>
     <t>OR</t>
@@ -1234,7 +1231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -1254,13 +1251,13 @@
         <v>20</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P2" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -1283,7 +1280,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -1303,7 +1300,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -1323,7 +1320,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -1349,7 +1346,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>34</v>
       </c>
@@ -1384,7 +1381,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
@@ -1404,7 +1401,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>42</v>
       </c>
@@ -1421,10 +1418,10 @@
         <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>22</v>
@@ -1433,7 +1430,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
@@ -1453,7 +1450,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>46</v>
       </c>
@@ -1464,7 +1461,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="E11" s="3">
         <v>100</v>
@@ -1491,7 +1488,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>51</v>
       </c>
@@ -1529,7 +1526,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>56</v>
       </c>
@@ -1555,7 +1552,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>60</v>
       </c>
@@ -1568,11 +1565,14 @@
       <c r="D14" s="11" t="s">
         <v>63</v>
       </c>
+      <c r="E14" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="P14" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>64</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>65</v>
       </c>
@@ -1605,11 +1605,14 @@
       <c r="D16" s="11" t="s">
         <v>63</v>
       </c>
+      <c r="E16" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="P16" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>66</v>
       </c>
@@ -1626,16 +1629,16 @@
         <v>80</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="P17" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>67</v>
       </c>
@@ -1658,7 +1661,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
@@ -1684,7 +1687,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>72</v>
       </c>
@@ -1697,8 +1700,8 @@
       <c r="D20" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="5">
-        <v>0.9</v>
+      <c r="E20" s="3">
+        <v>90</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="3" t="s">
@@ -1723,7 +1726,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>78</v>
       </c>
@@ -1740,16 +1743,16 @@
         <v>80</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="P21" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>79</v>
       </c>
@@ -1760,7 +1763,7 @@
         <v>80</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="E22" s="3">
         <v>20</v>
@@ -1806,14 +1809,17 @@
       <c r="D23" s="2" t="s">
         <v>63</v>
       </c>
+      <c r="E23" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="G23" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="144" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>84</v>
       </c>
@@ -1824,7 +1830,7 @@
         <v>86</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
@@ -1847,13 +1853,13 @@
         <v>80</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="E25" s="3">
         <v>100</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>89</v>
@@ -1865,7 +1871,7 @@
         <v>82</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>82</v>
@@ -1880,7 +1886,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>90</v>
       </c>
@@ -1891,7 +1897,7 @@
         <v>91</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E26" s="3">
         <v>100</v>
@@ -1906,7 +1912,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>92</v>
       </c>
@@ -1926,7 +1932,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>93</v>
       </c>
@@ -1946,7 +1952,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>95</v>
       </c>
@@ -1966,7 +1972,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>96</v>
       </c>
@@ -1983,10 +1989,10 @@
         <v>80</v>
       </c>
       <c r="G30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="P30" s="4">
         <v>46387</v>
@@ -2005,8 +2011,8 @@
       <c r="D31" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E31" s="5">
-        <v>0.7</v>
+      <c r="E31" s="3">
+        <v>70</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="3" t="s">
@@ -2083,13 +2089,13 @@
         <v>80</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="E33" s="3">
         <v>20</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P33" s="4">
         <v>46387</v>
@@ -2130,13 +2136,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P35" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>110</v>
       </c>
@@ -2174,7 +2180,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>119</v>
       </c>
@@ -2212,7 +2218,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>123</v>
       </c>
@@ -2250,12 +2256,12 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>112</v>
@@ -2288,9 +2294,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>111</v>
@@ -2305,13 +2311,13 @@
         <v>100</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P40" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>78</v>
       </c>
@@ -2351,25 +2357,33 @@
     </row>
     <row r="42" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="1"/>
+      <c r="C42" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
       <c r="P42" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>75</v>
@@ -2383,14 +2397,17 @@
     </row>
     <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="P44" s="4">
         <v>46387</v>
@@ -2398,41 +2415,62 @@
     </row>
     <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
       <c r="P45" s="4">
         <v>46387</v>
       </c>
     </row>
     <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
       <c r="P46" s="4">
         <v>46387</v>
       </c>
     </row>
     <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C47" s="1"/>
+      <c r="C47" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="D47" s="11" t="s">
         <v>23</v>
       </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
       <c r="G47" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P47" s="4">
         <v>46387</v>
@@ -2440,22 +2478,22 @@
     </row>
     <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="D48" s="11" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="E48" s="3">
         <v>50</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>33</v>
@@ -2482,15 +2520,15 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>113</v>
@@ -2520,18 +2558,18 @@
         <v>116</v>
       </c>
       <c r="O49" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="P49" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="P49" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>36</v>
@@ -2549,7 +2587,7 @@
         <v>33</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>116</v>
@@ -2567,9 +2605,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>29</v>
@@ -2578,22 +2616,22 @@
         <v>30</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="E51" s="3">
         <v>100</v>
       </c>
       <c r="G51" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="J51" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="J51" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="K51" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P51" s="3" t="s">
         <v>33</v>
@@ -2601,7 +2639,7 @@
     </row>
     <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>29</v>
@@ -2616,21 +2654,21 @@
         <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>113</v>
@@ -2645,19 +2683,19 @@
         <v>116</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P53" s="4"/>
     </row>
-    <row r="54" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>113</v>
@@ -2672,10 +2710,10 @@
         <v>33</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>116</v>
@@ -2687,9 +2725,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>22</v>
@@ -2707,9 +2745,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>22</v>
@@ -2727,15 +2765,15 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>23</v>
@@ -2747,9 +2785,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>22</v>
@@ -2767,9 +2805,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>22</v>
@@ -2787,15 +2825,15 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>113</v>
@@ -2804,7 +2842,7 @@
         <v>100</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>116</v>
@@ -2813,19 +2851,19 @@
         <v>116</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P60" s="4"/>
     </row>
-    <row r="61" spans="1:16" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" ht="144" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>37</v>
@@ -2834,10 +2872,10 @@
         <v>100</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P61" s="4">
         <v>46387</v>
@@ -2845,33 +2883,33 @@
     </row>
     <row r="62" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>75</v>
       </c>
       <c r="E62" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P62" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>36</v>
@@ -2883,16 +2921,16 @@
         <v>100</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>39</v>
@@ -2907,18 +2945,18 @@
         <v>82</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P63" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>118</v>
@@ -2944,7 +2982,7 @@
     </row>
     <row r="65" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>107</v>
@@ -2959,21 +2997,21 @@
         <v>22</v>
       </c>
       <c r="G65" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="P65" s="4">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="P65" s="4">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D66" s="11" t="s">
         <v>23</v>
@@ -3004,15 +3042,15 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>23</v>
@@ -3043,9 +3081,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>98</v>
@@ -3064,7 +3102,7 @@
         <v>54</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>76</v>
@@ -3085,9 +3123,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>61</v>
@@ -3098,15 +3136,20 @@
       <c r="D69" s="11" t="s">
         <v>63</v>
       </c>
+      <c r="E69" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="P69" s="3" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P69" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
-    <filterColumn colId="1">
+    <filterColumn colId="4">
       <filters>
-        <filter val="Soumya"/>
+        <filter val="100"/>
+        <filter val="80"/>
+        <filter val="90"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3121,15 +3164,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -3152,7 +3186,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020CF8294E4C5A44CB8AF60CE499E006F" ma:contentTypeVersion="32" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="009ade30d862eccbd4a375ee527febd2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="5624914c-2aad-4993-a320-2eb67911e80a" xmlns:ns3="41fb0f91-a3b9-4963-8e6c-81696287e595" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a2a584ab283d97548660d8e8b35cff3" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3498,15 +3532,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DABEB6D-3BAD-47AB-9B08-E3D505D0C37F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF7AA70-C622-4509-9661-E5AB3E79D417}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3518,7 +3553,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{062249BE-4AA3-4403-8E45-C85EF69B7519}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3536,4 +3571,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DABEB6D-3BAD-47AB-9B08-E3D505D0C37F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/KT Compliance.xlsx
+++ b/KT Compliance.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://powerschoolgroup-my.sharepoint.com/personal/prabha_parthasarathy_powerschool_com/Documents/GPM/2026/KT 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="817" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D668E19F-7167-4A4F-9CFF-B80BE7F54FDD}"/>
+  <xr:revisionPtr revIDLastSave="1214" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D887D144-2CC1-4AAE-89CF-2D82ABBC31EF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B7FEA37-02A6-41FF-9931-0A86E2A764FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Q3 status" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Q3 status'!$A$1:$K$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$P$69</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -44,11 +46,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={C0ACCDE5-39A1-443F-AFAB-06CD4B5AF659}</author>
-    <author>tc={2444CFCC-5DB3-4AD6-AA9D-9D23ACFB4185}</author>
+    <author>tc={A943E5F1-9C28-4DC4-B620-6E432F3332C1}</author>
+    <author>tc={AD3794B6-02BF-46F2-B4D4-9194931335F3}</author>
   </authors>
   <commentList>
-    <comment ref="A32" authorId="0" shapeId="0" xr:uid="{C0ACCDE5-39A1-443F-AFAB-06CD4B5AF659}">
+    <comment ref="A32" authorId="0" shapeId="0" xr:uid="{A943E5F1-9C28-4DC4-B620-6E432F3332C1}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -57,7 +59,35 @@
 </t>
       </text>
     </comment>
-    <comment ref="A44" authorId="1" shapeId="0" xr:uid="{2444CFCC-5DB3-4AD6-AA9D-9D23ACFB4185}">
+    <comment ref="A44" authorId="1" shapeId="0" xr:uid="{AD3794B6-02BF-46F2-B4D4-9194931335F3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Last year of support</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={46F2D948-24A2-49D6-BE84-0478FDF76271}</author>
+    <author>tc={0F641077-B796-4938-9B3E-5D72CED7DFB1}</author>
+  </authors>
+  <commentList>
+    <comment ref="A32" authorId="0" shapeId="0" xr:uid="{46F2D948-24A2-49D6-BE84-0478FDF76271}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Last year of support
+</t>
+      </text>
+    </comment>
+    <comment ref="A44" authorId="1" shapeId="0" xr:uid="{0F641077-B796-4938-9B3E-5D72CED7DFB1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -70,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="196">
   <si>
     <t>Product Area</t>
   </si>
@@ -262,9 +292,6 @@
     <t>MO</t>
   </si>
   <si>
-    <t>Anuj</t>
-  </si>
-  <si>
     <t>Jessica / Turab</t>
   </si>
   <si>
@@ -304,18 +331,12 @@
     <t>OK</t>
   </si>
   <si>
-    <t xml:space="preserve">Anuj </t>
-  </si>
-  <si>
     <t>VT</t>
   </si>
   <si>
     <t>Ajish</t>
   </si>
   <si>
-    <t>Vette/Newhire</t>
-  </si>
-  <si>
     <t>Not started</t>
   </si>
   <si>
@@ -334,9 +355,6 @@
     <t>Michael</t>
   </si>
   <si>
-    <t>All</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -352,9 +370,6 @@
     <t>Fred</t>
   </si>
   <si>
-    <t>Had a discussion with Debra! MD will be taken by Prashu and Debra and PA will be taken by Fred. Have a sync up call on 18th May to discuss. In a nutshell KT not required.</t>
-  </si>
-  <si>
     <t>UT</t>
   </si>
   <si>
@@ -364,9 +379,6 @@
     <t>MS</t>
   </si>
   <si>
-    <t>Jessica/Caron*</t>
-  </si>
-  <si>
     <t>ON</t>
   </si>
   <si>
@@ -388,9 +400,6 @@
     <t>Ankit</t>
   </si>
   <si>
-    <t>Fred/Newhire</t>
-  </si>
-  <si>
     <t>Sif Unity, IA current backlog and future commitments</t>
   </si>
   <si>
@@ -418,9 +427,6 @@
     <t>NY</t>
   </si>
   <si>
-    <t>Shereen/NewHire</t>
-  </si>
-  <si>
     <t>CA(esp)</t>
   </si>
   <si>
@@ -433,9 +439,6 @@
     <t>Completed</t>
   </si>
   <si>
-    <t>Prashu gave this to Rohan few months back and its given back.</t>
-  </si>
-  <si>
     <t>1 ticket ongoing communcaiton with customer. To be clarified with customers</t>
   </si>
   <si>
@@ -451,9 +454,6 @@
     <t>MD(esp)</t>
   </si>
   <si>
-    <t>completed</t>
-  </si>
-  <si>
     <t>done</t>
   </si>
   <si>
@@ -463,9 +463,6 @@
     <t>NJ(esp)</t>
   </si>
   <si>
-    <t>Prashu gave this to Rajesh few months back and its now coming back</t>
-  </si>
-  <si>
     <t>No KT required, Prashu is already taking care of this</t>
   </si>
   <si>
@@ -473,9 +470,6 @@
   </si>
   <si>
     <t>OR</t>
-  </si>
-  <si>
-    <t>Prashu Already handling OR state since Feb 2026</t>
   </si>
   <si>
     <t xml:space="preserve">CRDC
@@ -515,9 +509,6 @@
     <t>Caron*</t>
   </si>
   <si>
-    <t>Everything</t>
-  </si>
-  <si>
     <t>WA</t>
   </si>
   <si>
@@ -539,10 +530,6 @@
     <t>CT</t>
   </si>
   <si>
-    <t>Backlog
-Recent development</t>
-  </si>
-  <si>
     <t xml:space="preserve"> FG &amp; UG Calls handled by Jessica</t>
   </si>
   <si>
@@ -592,9 +579,6 @@
   </si>
   <si>
     <t>NE</t>
-  </si>
-  <si>
-    <t>Turab/ Caron*</t>
   </si>
   <si>
     <t>CA</t>
@@ -634,9 +618,6 @@
 </t>
   </si>
   <si>
-    <t>Micheal will start from Q3/Q4</t>
-  </si>
-  <si>
     <t>KT not started</t>
   </si>
   <si>
@@ -644,9 +625,6 @@
   </si>
   <si>
     <t>Not planned</t>
-  </si>
-  <si>
-    <t>Ticket handling with India team by Alka</t>
   </si>
   <si>
     <t>Shannita handles all customer intercations</t>
@@ -665,17 +643,80 @@
 Chhaya is part of all calls with customer and handling tickets.</t>
   </si>
   <si>
-    <t>July - Micheal is yet to start customer calls or ticket handling</t>
-  </si>
-  <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>Grooming</t>
+  </si>
+  <si>
+    <t>Demos</t>
+  </si>
+  <si>
+    <t>Customer slides</t>
+  </si>
+  <si>
+    <t>Customer calls</t>
+  </si>
+  <si>
+    <t>Release notes</t>
+  </si>
+  <si>
+    <t>Dev clarifications</t>
+  </si>
+  <si>
+    <t>Bugs / support calls</t>
+  </si>
+  <si>
+    <t>Customer calls for new reqs.</t>
+  </si>
+  <si>
+    <t>US PM Vacation/ Conference support</t>
+  </si>
+  <si>
+    <t>Robyn</t>
+  </si>
+  <si>
+    <t>Regina</t>
+  </si>
+  <si>
+    <t>Prisana Shaw</t>
+  </si>
+  <si>
+    <t>Jason</t>
+  </si>
+  <si>
+    <t>Caron</t>
+  </si>
+  <si>
+    <t>Anuj/ Jessica</t>
+  </si>
+  <si>
+    <t>Anuj /Turab</t>
+  </si>
+  <si>
+    <t>Anuj/Jessica</t>
+  </si>
+  <si>
+    <t>Dan</t>
+  </si>
+  <si>
+    <t>New requirements/tickets</t>
+  </si>
+  <si>
+    <t>LOST</t>
+  </si>
+  <si>
+    <t>Regina/Vette</t>
+  </si>
+  <si>
+    <t>Vette/Regina</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -713,6 +754,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -734,7 +781,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -757,12 +804,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -805,6 +863,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1148,11 +1212,23 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A32" dT="2024-12-05T16:51:01.05" personId="{D3206E26-97D1-4EED-9A9C-AC1B96B26E03}" id="{C0ACCDE5-39A1-443F-AFAB-06CD4B5AF659}">
+  <threadedComment ref="A32" dT="2024-12-05T16:51:01.05" personId="{D3206E26-97D1-4EED-9A9C-AC1B96B26E03}" id="{A943E5F1-9C28-4DC4-B620-6E432F3332C1}">
     <text xml:space="preserve">Last year of support
 </text>
   </threadedComment>
-  <threadedComment ref="A44" dT="2024-12-05T16:50:38.65" personId="{D3206E26-97D1-4EED-9A9C-AC1B96B26E03}" id="{2444CFCC-5DB3-4AD6-AA9D-9D23ACFB4185}">
+  <threadedComment ref="A44" dT="2024-12-05T16:50:38.65" personId="{D3206E26-97D1-4EED-9A9C-AC1B96B26E03}" id="{AD3794B6-02BF-46F2-B4D4-9194931335F3}">
+    <text>Last year of support</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A32" dT="2024-12-05T16:51:01.05" personId="{D3206E26-97D1-4EED-9A9C-AC1B96B26E03}" id="{46F2D948-24A2-49D6-BE84-0478FDF76271}">
+    <text xml:space="preserve">Last year of support
+</text>
+  </threadedComment>
+  <threadedComment ref="A44" dT="2024-12-05T16:50:38.65" personId="{D3206E26-97D1-4EED-9A9C-AC1B96B26E03}" id="{0F641077-B796-4938-9B3E-5D72CED7DFB1}">
     <text>Last year of support</text>
   </threadedComment>
 </ThreadedComments>
@@ -1160,7 +1236,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P69"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1251,7 +1326,7 @@
         <v>20</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="P2" s="4">
         <v>46387</v>
@@ -1334,7 +1409,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>31</v>
@@ -1354,7 +1429,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>37</v>
@@ -1415,13 +1490,10 @@
         <v>23</v>
       </c>
       <c r="E9" s="3">
-        <v>80</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>22</v>
@@ -1461,7 +1533,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E11" s="3">
         <v>100</v>
@@ -1531,10 +1603,10 @@
         <v>56</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>23</v>
@@ -1546,24 +1618,24 @@
         <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P13" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>22</v>
@@ -1574,7 +1646,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>22</v>
@@ -1592,18 +1664,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>63</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>22</v>
@@ -1614,7 +1686,7 @@
     </row>
     <row r="17" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>43</v>
@@ -1626,13 +1698,13 @@
         <v>23</v>
       </c>
       <c r="E17" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>54</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="P17" s="4">
         <v>46387</v>
@@ -1640,13 +1712,13 @@
     </row>
     <row r="18" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>19</v>
@@ -1655,7 +1727,7 @@
         <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P18" s="4">
         <v>46387</v>
@@ -1663,13 +1735,13 @@
     </row>
     <row r="19" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>19</v>
@@ -1681,46 +1753,31 @@
         <v>33</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P19" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>75</v>
-      </c>
       <c r="E20" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P20" s="4">
         <v>46387</v>
@@ -1728,7 +1785,7 @@
     </row>
     <row r="21" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>43</v>
@@ -1740,65 +1797,62 @@
         <v>23</v>
       </c>
       <c r="E21" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>54</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="P21" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="E22" s="3">
-        <v>20</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>33</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>29</v>
@@ -1807,80 +1861,74 @@
         <v>22</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="144" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="P24" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E25" s="3">
         <v>100</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="H25" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>33</v>
@@ -1888,25 +1936,22 @@
     </row>
     <row r="26" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>57</v>
+        <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="E26" s="3">
         <v>100</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P26" s="4">
         <v>46185</v>
@@ -1914,7 +1959,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>22</v>
@@ -1934,13 +1979,13 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>23</v>
@@ -1954,13 +1999,13 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>23</v>
@@ -1972,9 +2017,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>43</v>
@@ -1986,131 +2031,125 @@
         <v>23</v>
       </c>
       <c r="E30" s="3">
-        <v>80</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="P30" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="E31" s="3">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="P31" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="P32" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>37</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="P33" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E34" s="3">
         <v>0</v>
@@ -2119,24 +2158,24 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>109</v>
+        <v>184</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="P35" s="4">
         <v>46387</v>
@@ -2144,37 +2183,34 @@
     </row>
     <row r="36" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E36" s="3">
         <v>100</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="I36" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="P36" s="4">
         <v>46387</v>
@@ -2182,63 +2218,57 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E37" s="3">
+        <v>100</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="O37" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" s="3">
-        <v>100</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="P37" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E38" s="3">
         <v>100</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="I38" s="3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>22</v>
@@ -2247,71 +2277,65 @@
         <v>22</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="P38" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" s="3">
+        <v>100</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="O39" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="3">
-        <v>100</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="P39" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E40" s="3">
         <v>100</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="P40" s="4">
         <v>46387</v>
@@ -2319,13 +2343,13 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>23</v>
@@ -2333,11 +2357,8 @@
       <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="I41" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>22</v>
@@ -2346,27 +2367,27 @@
         <v>22</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="P41" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2377,16 +2398,16 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
@@ -2395,36 +2416,36 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="11" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
       <c r="P44" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -2433,18 +2454,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E46" s="3">
         <v>0</v>
@@ -2453,15 +2474,15 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>23</v>
@@ -2470,30 +2491,27 @@
         <v>0</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="P47" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>37</v>
       </c>
       <c r="E48" s="3">
-        <v>50</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>33</v>
@@ -2508,13 +2526,13 @@
         <v>33</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P48" s="4">
         <v>46387</v>
@@ -2522,16 +2540,16 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E49" s="3">
         <v>100</v>
@@ -2539,9 +2557,6 @@
       <c r="F49" s="12">
         <v>46174</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>33</v>
       </c>
@@ -2549,16 +2564,16 @@
         <v>33</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="P49" s="4">
         <v>46387</v>
@@ -2566,16 +2581,16 @@
     </row>
     <row r="50" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E50" s="3">
         <v>100</v>
@@ -2583,20 +2598,17 @@
       <c r="F50" s="12">
         <v>46174</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="I50" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>40</v>
@@ -2605,9 +2617,9 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>29</v>
@@ -2616,45 +2628,42 @@
         <v>30</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E51" s="3">
         <v>100</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="I51" s="3" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="P51" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>33</v>
@@ -2662,43 +2671,43 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E53" s="3">
         <v>100</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="P53" s="4"/>
     </row>
     <row r="54" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E54" s="15">
         <v>100</v>
@@ -2706,20 +2715,17 @@
       <c r="F54" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="H54" s="3" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="P54" s="4">
         <v>46387</v>
@@ -2727,13 +2733,13 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>23</v>
@@ -2747,13 +2753,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>23</v>
@@ -2767,13 +2773,13 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>23</v>
@@ -2787,13 +2793,13 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>23</v>
@@ -2807,13 +2813,13 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>23</v>
@@ -2827,43 +2833,43 @@
     </row>
     <row r="60" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E60" s="15">
         <v>100</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="P60" s="4"/>
     </row>
     <row r="61" spans="1:16" ht="144" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>37</v>
@@ -2872,33 +2878,33 @@
         <v>100</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="P61" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="P62" s="4">
         <v>46387</v>
@@ -2906,46 +2912,46 @@
     </row>
     <row r="63" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E63" s="3">
         <v>100</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>39</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="P63" s="4">
         <v>46387</v>
@@ -2953,13 +2959,13 @@
     </row>
     <row r="64" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>23</v>
@@ -2980,15 +2986,15 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>23</v>
@@ -2997,7 +3003,7 @@
         <v>22</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="P65" s="4">
         <v>46387</v>
@@ -3005,13 +3011,13 @@
     </row>
     <row r="66" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D66" s="11" t="s">
         <v>23</v>
@@ -3024,19 +3030,19 @@
         <v>54</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P66" s="4">
         <v>46387</v>
@@ -3044,13 +3050,13 @@
     </row>
     <row r="67" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>23</v>
@@ -3063,19 +3069,19 @@
         <v>54</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P67" s="4">
         <v>46387</v>
@@ -3083,13 +3089,13 @@
     </row>
     <row r="68" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D68" s="11" t="s">
         <v>23</v>
@@ -3102,39 +3108,39 @@
         <v>54</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="P68" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="D69" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>63</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>22</v>
@@ -3144,15 +3150,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P69" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="100"/>
-        <filter val="80"/>
-        <filter val="90"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:P69" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}"/>
   <hyperlinks>
     <hyperlink ref="J54" r:id="rId1" xr:uid="{5DBA3A74-260E-4C5A-B9BA-696E7347EBA4}"/>
     <hyperlink ref="J60" r:id="rId2" xr:uid="{2A438ECF-BCA9-41C5-8312-3C3516217E53}"/>
@@ -3163,27 +3161,3062 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F205A0C-46CE-4182-BB45-6DE4405E370B}">
+  <dimension ref="A1:P69"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19" style="11" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="P1" s="16"/>
+    </row>
+    <row r="2" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>30</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>30</v>
+      </c>
+      <c r="K2">
+        <v>50</v>
+      </c>
+      <c r="L2">
+        <v>30</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3">
+        <v>100</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="3">
+        <v>100</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3">
+        <v>100</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
+        <v>80</v>
+      </c>
+      <c r="M9">
+        <v>50</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="3">
+        <v>100</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="3">
+        <v>90</v>
+      </c>
+      <c r="F12">
+        <v>80</v>
+      </c>
+      <c r="G12">
+        <v>80</v>
+      </c>
+      <c r="H12">
+        <v>50</v>
+      </c>
+      <c r="I12">
+        <v>20</v>
+      </c>
+      <c r="J12">
+        <v>50</v>
+      </c>
+      <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
+        <v>100</v>
+      </c>
+      <c r="M12">
+        <v>50</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="3">
+        <v>100</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="3">
+        <v>100</v>
+      </c>
+      <c r="F17">
+        <v>80</v>
+      </c>
+      <c r="G17">
+        <v>50</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>20</v>
+      </c>
+      <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
+        <v>80</v>
+      </c>
+      <c r="M17">
+        <v>50</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="3">
+        <v>100</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="3">
+        <v>100</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20">
+        <v>100</v>
+      </c>
+      <c r="H20">
+        <v>100</v>
+      </c>
+      <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20">
+        <v>90</v>
+      </c>
+      <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
+        <v>100</v>
+      </c>
+      <c r="M20">
+        <v>75</v>
+      </c>
+      <c r="N20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21">
+        <v>80</v>
+      </c>
+      <c r="G21">
+        <v>50</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>20</v>
+      </c>
+      <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
+        <v>80</v>
+      </c>
+      <c r="M21">
+        <v>50</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="3">
+        <v>100</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="G22">
+        <v>50</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>100</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" s="3">
+        <v>100</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+      <c r="G25">
+        <v>50</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>100</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="3">
+        <v>100</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="3">
+        <v>100</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="3">
+        <v>100</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="3">
+        <v>100</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="3">
+        <v>100</v>
+      </c>
+      <c r="F30">
+        <v>80</v>
+      </c>
+      <c r="G30">
+        <v>50</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
+        <v>80</v>
+      </c>
+      <c r="M30">
+        <v>50</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31">
+        <v>100</v>
+      </c>
+      <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="3">
+        <v>100</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="G34">
+        <v>100</v>
+      </c>
+      <c r="H34">
+        <v>100</v>
+      </c>
+      <c r="I34">
+        <v>100</v>
+      </c>
+      <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
+        <v>100</v>
+      </c>
+      <c r="M34">
+        <v>100</v>
+      </c>
+      <c r="N34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>100</v>
+      </c>
+      <c r="G35">
+        <v>100</v>
+      </c>
+      <c r="H35">
+        <v>100</v>
+      </c>
+      <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
+        <v>100</v>
+      </c>
+      <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
+        <v>100</v>
+      </c>
+      <c r="M35">
+        <v>100</v>
+      </c>
+      <c r="N35">
+        <v>100</v>
+      </c>
+      <c r="O35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="3">
+        <v>100</v>
+      </c>
+      <c r="F36">
+        <v>100</v>
+      </c>
+      <c r="G36">
+        <v>100</v>
+      </c>
+      <c r="H36">
+        <v>100</v>
+      </c>
+      <c r="I36">
+        <v>100</v>
+      </c>
+      <c r="J36">
+        <v>100</v>
+      </c>
+      <c r="K36">
+        <v>100</v>
+      </c>
+      <c r="L36">
+        <v>100</v>
+      </c>
+      <c r="M36">
+        <v>100</v>
+      </c>
+      <c r="N36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E37" s="3">
+        <v>100</v>
+      </c>
+      <c r="F37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" t="s">
+        <v>22</v>
+      </c>
+      <c r="K37" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" s="3">
+        <v>100</v>
+      </c>
+      <c r="F38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" t="s">
+        <v>22</v>
+      </c>
+      <c r="L38" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" s="3">
+        <v>100</v>
+      </c>
+      <c r="F39">
+        <v>100</v>
+      </c>
+      <c r="G39">
+        <v>100</v>
+      </c>
+      <c r="H39">
+        <v>100</v>
+      </c>
+      <c r="I39">
+        <v>100</v>
+      </c>
+      <c r="J39">
+        <v>100</v>
+      </c>
+      <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
+        <v>100</v>
+      </c>
+      <c r="M39">
+        <v>100</v>
+      </c>
+      <c r="N39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E40" s="3">
+        <v>100</v>
+      </c>
+      <c r="F40">
+        <v>100</v>
+      </c>
+      <c r="G40">
+        <v>100</v>
+      </c>
+      <c r="H40">
+        <v>100</v>
+      </c>
+      <c r="I40">
+        <v>100</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+      <c r="K40">
+        <v>100</v>
+      </c>
+      <c r="L40">
+        <v>100</v>
+      </c>
+      <c r="M40">
+        <v>100</v>
+      </c>
+      <c r="N40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="3">
+        <v>100</v>
+      </c>
+      <c r="F41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" t="s">
+        <v>22</v>
+      </c>
+      <c r="L41" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" t="s">
+        <v>22</v>
+      </c>
+      <c r="N41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>100</v>
+      </c>
+      <c r="G42">
+        <v>100</v>
+      </c>
+      <c r="H42">
+        <v>100</v>
+      </c>
+      <c r="I42">
+        <v>100</v>
+      </c>
+      <c r="J42">
+        <v>100</v>
+      </c>
+      <c r="K42">
+        <v>100</v>
+      </c>
+      <c r="L42">
+        <v>100</v>
+      </c>
+      <c r="M42">
+        <v>100</v>
+      </c>
+      <c r="N42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43">
+        <v>100</v>
+      </c>
+      <c r="G43">
+        <v>100</v>
+      </c>
+      <c r="H43">
+        <v>100</v>
+      </c>
+      <c r="I43">
+        <v>100</v>
+      </c>
+      <c r="J43">
+        <v>100</v>
+      </c>
+      <c r="K43">
+        <v>100</v>
+      </c>
+      <c r="L43">
+        <v>100</v>
+      </c>
+      <c r="M43">
+        <v>100</v>
+      </c>
+      <c r="N43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="G45">
+        <v>100</v>
+      </c>
+      <c r="H45">
+        <v>100</v>
+      </c>
+      <c r="I45">
+        <v>100</v>
+      </c>
+      <c r="J45">
+        <v>100</v>
+      </c>
+      <c r="K45">
+        <v>100</v>
+      </c>
+      <c r="L45">
+        <v>100</v>
+      </c>
+      <c r="M45">
+        <v>100</v>
+      </c>
+      <c r="N45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>100</v>
+      </c>
+      <c r="G46">
+        <v>100</v>
+      </c>
+      <c r="H46">
+        <v>100</v>
+      </c>
+      <c r="I46">
+        <v>100</v>
+      </c>
+      <c r="J46">
+        <v>100</v>
+      </c>
+      <c r="K46">
+        <v>100</v>
+      </c>
+      <c r="L46">
+        <v>100</v>
+      </c>
+      <c r="M46">
+        <v>100</v>
+      </c>
+      <c r="N46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E48" s="3">
+        <v>100</v>
+      </c>
+      <c r="F48">
+        <v>100</v>
+      </c>
+      <c r="G48">
+        <v>100</v>
+      </c>
+      <c r="H48">
+        <v>100</v>
+      </c>
+      <c r="I48">
+        <v>100</v>
+      </c>
+      <c r="J48">
+        <v>100</v>
+      </c>
+      <c r="K48">
+        <v>50</v>
+      </c>
+      <c r="L48">
+        <v>100</v>
+      </c>
+      <c r="M48">
+        <v>50</v>
+      </c>
+      <c r="N48">
+        <v>80</v>
+      </c>
+      <c r="O48">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E49" s="3">
+        <v>100</v>
+      </c>
+      <c r="F49">
+        <v>100</v>
+      </c>
+      <c r="G49">
+        <v>100</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>20</v>
+      </c>
+      <c r="K49">
+        <v>50</v>
+      </c>
+      <c r="L49">
+        <v>50</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E50" s="3">
+        <v>100</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>100</v>
+      </c>
+      <c r="H50">
+        <v>20</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>30</v>
+      </c>
+      <c r="L50">
+        <v>50</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E51" s="3">
+        <v>100</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>100</v>
+      </c>
+      <c r="G52">
+        <v>100</v>
+      </c>
+      <c r="H52">
+        <v>100</v>
+      </c>
+      <c r="I52">
+        <v>100</v>
+      </c>
+      <c r="J52">
+        <v>100</v>
+      </c>
+      <c r="K52">
+        <v>100</v>
+      </c>
+      <c r="L52">
+        <v>100</v>
+      </c>
+      <c r="M52">
+        <v>100</v>
+      </c>
+      <c r="N52">
+        <v>100</v>
+      </c>
+      <c r="O52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E53" s="3">
+        <v>100</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E54" s="15">
+        <v>100</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="15">
+        <v>100</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J55" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K55" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L55" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M55" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="15">
+        <v>100</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K56" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L56" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M56" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="15">
+        <v>100</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K57" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L57" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M57" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" s="15">
+        <v>100</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K58" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L58" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M58" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="15">
+        <v>100</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J59" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L59" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M59" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E60" s="15">
+        <v>100</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>100</v>
+      </c>
+      <c r="G62">
+        <v>100</v>
+      </c>
+      <c r="H62">
+        <v>100</v>
+      </c>
+      <c r="I62">
+        <v>100</v>
+      </c>
+      <c r="J62">
+        <v>100</v>
+      </c>
+      <c r="K62">
+        <v>100</v>
+      </c>
+      <c r="L62">
+        <v>100</v>
+      </c>
+      <c r="M62">
+        <v>100</v>
+      </c>
+      <c r="N62">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E63" s="3">
+        <v>100</v>
+      </c>
+      <c r="F63">
+        <v>100</v>
+      </c>
+      <c r="G63">
+        <v>100</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>20</v>
+      </c>
+      <c r="K63">
+        <v>50</v>
+      </c>
+      <c r="L63">
+        <v>50</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" s="3">
+        <v>80</v>
+      </c>
+      <c r="F64">
+        <v>100</v>
+      </c>
+      <c r="G64">
+        <v>100</v>
+      </c>
+      <c r="H64">
+        <v>100</v>
+      </c>
+      <c r="I64">
+        <v>30</v>
+      </c>
+      <c r="J64">
+        <v>50</v>
+      </c>
+      <c r="K64">
+        <v>100</v>
+      </c>
+      <c r="L64">
+        <v>100</v>
+      </c>
+      <c r="M64">
+        <v>100</v>
+      </c>
+      <c r="N64">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F65" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" t="s">
+        <v>22</v>
+      </c>
+      <c r="H65" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K65" t="s">
+        <v>22</v>
+      </c>
+      <c r="L65" t="s">
+        <v>22</v>
+      </c>
+      <c r="M65" t="s">
+        <v>22</v>
+      </c>
+      <c r="N65" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="3">
+        <v>90</v>
+      </c>
+      <c r="F66">
+        <v>100</v>
+      </c>
+      <c r="G66">
+        <v>100</v>
+      </c>
+      <c r="H66">
+        <v>50</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>25</v>
+      </c>
+      <c r="K66">
+        <v>100</v>
+      </c>
+      <c r="L66">
+        <v>50</v>
+      </c>
+      <c r="M66">
+        <v>50</v>
+      </c>
+      <c r="N66">
+        <v>20</v>
+      </c>
+      <c r="O66">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="3">
+        <v>90</v>
+      </c>
+      <c r="F67">
+        <v>100</v>
+      </c>
+      <c r="G67">
+        <v>100</v>
+      </c>
+      <c r="H67">
+        <v>50</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>100</v>
+      </c>
+      <c r="L67">
+        <v>50</v>
+      </c>
+      <c r="M67">
+        <v>30</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="3">
+        <v>80</v>
+      </c>
+      <c r="F68">
+        <v>100</v>
+      </c>
+      <c r="G68">
+        <v>100</v>
+      </c>
+      <c r="H68">
+        <v>80</v>
+      </c>
+      <c r="I68">
+        <v>80</v>
+      </c>
+      <c r="J68">
+        <v>80</v>
+      </c>
+      <c r="K68">
+        <v>100</v>
+      </c>
+      <c r="L68">
+        <v>100</v>
+      </c>
+      <c r="M68">
+        <v>80</v>
+      </c>
+      <c r="N68">
+        <v>80</v>
+      </c>
+      <c r="O68">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K69" xr:uid="{0F205A0C-46CE-4182-BB45-6DE4405E370B}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Demogivenby xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <DemoBy xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <Comments0 xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <TaxCatchAll xmlns="5624914c-2aad-4993-a320-2eb67911e80a" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <ZoomPassword xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Demodate xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <JiraTicket xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <Comments xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <TicketNumbers xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <Demodated xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3533,22 +6566,32 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Demogivenby xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <DemoBy xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Comments0 xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <TaxCatchAll xmlns="5624914c-2aad-4993-a320-2eb67911e80a" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <ZoomPassword xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Demodate xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <JiraTicket xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Comments xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <TicketNumbers xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Demodated xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF7AA70-C622-4509-9661-E5AB3E79D417}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DABEB6D-3BAD-47AB-9B08-E3D505D0C37F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="41fb0f91-a3b9-4963-8e6c-81696287e595"/>
-    <ds:schemaRef ds:uri="5624914c-2aad-4993-a320-2eb67911e80a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3574,9 +6617,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DABEB6D-3BAD-47AB-9B08-E3D505D0C37F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF7AA70-C622-4509-9661-E5AB3E79D417}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="41fb0f91-a3b9-4963-8e6c-81696287e595"/>
+    <ds:schemaRef ds:uri="5624914c-2aad-4993-a320-2eb67911e80a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/KT Compliance.xlsx
+++ b/KT Compliance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://powerschoolgroup-my.sharepoint.com/personal/prabha_parthasarathy_powerschool_com/Documents/GPM/2026/KT 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1214" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D887D144-2CC1-4AAE-89CF-2D82ABBC31EF}"/>
+  <xr:revisionPtr revIDLastSave="1266" documentId="8_{EEADC8E9-AC76-4B63-BCAA-4AAF86FA836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35837377-6DC4-4E9D-BD4A-AFA67FB64112}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B7FEA37-02A6-41FF-9931-0A86E2A764FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8B7FEA37-02A6-41FF-9931-0A86E2A764FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="194">
   <si>
     <t>Product Area</t>
   </si>
@@ -183,6 +183,10 @@
     <t>SIF Unity parallel coming up.</t>
   </si>
   <si>
+    <t>SIF Unity tickets created.
+Chhaya is part of all calls with customer and handling tickets.</t>
+  </si>
+  <si>
     <t>MI Ed-Fi</t>
   </si>
   <si>
@@ -228,7 +232,7 @@
     <t>Chintan</t>
   </si>
   <si>
-    <t>Jason*</t>
+    <t>Jason</t>
   </si>
   <si>
     <t>In process</t>
@@ -255,6 +259,9 @@
     <t>ShanNita</t>
   </si>
   <si>
+    <t>Shannita handles all customer intercations</t>
+  </si>
+  <si>
     <t>WI Ed-Fi</t>
   </si>
   <si>
@@ -264,6 +271,9 @@
     <t>NA / Turab</t>
   </si>
   <si>
+    <t>Completed</t>
+  </si>
+  <si>
     <t>May</t>
   </si>
   <si>
@@ -277,9 +287,6 @@
   </si>
   <si>
     <t>Prabha</t>
-  </si>
-  <si>
-    <t>Vette *</t>
   </si>
   <si>
     <t>Current Backlog, 
@@ -292,6 +299,9 @@
     <t>MO</t>
   </si>
   <si>
+    <t>Anuj/ Jessica</t>
+  </si>
+  <si>
     <t>Jessica / Turab</t>
   </si>
   <si>
@@ -331,87 +341,108 @@
     <t>OK</t>
   </si>
   <si>
+    <t>Anuj /Turab</t>
+  </si>
+  <si>
+    <t>Prisana Shaw</t>
+  </si>
+  <si>
     <t>VT</t>
   </si>
   <si>
     <t>Ajish</t>
   </si>
   <si>
+    <t>Vette/Regina</t>
+  </si>
+  <si>
     <t>Not started</t>
   </si>
   <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>UDC</t>
+  </si>
+  <si>
+    <t>Not planned</t>
+  </si>
+  <si>
+    <t>TX(esp)</t>
+  </si>
+  <si>
+    <t>Rajesh (eSP)</t>
+  </si>
+  <si>
+    <t>Fred</t>
+  </si>
+  <si>
+    <t>UT</t>
+  </si>
+  <si>
+    <t>Utah backpack live date is end of May and is at risk</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Anuj/Jessica</t>
+  </si>
+  <si>
+    <t>Caron</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>MBA</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>Ankit</t>
+  </si>
+  <si>
+    <t>Sif Unity, IA current backlog and future commitments</t>
+  </si>
+  <si>
+    <t>Sif Unity yearcoming up.</t>
+  </si>
+  <si>
     <t>Not required</t>
   </si>
   <si>
-    <t>Vette leads all meetings</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>UDC</t>
-  </si>
-  <si>
-    <t>TX(esp)</t>
-  </si>
-  <si>
-    <t>Rajesh (eSP)</t>
-  </si>
-  <si>
-    <t>Fred</t>
-  </si>
-  <si>
-    <t>UT</t>
-  </si>
-  <si>
-    <t>Utah backpack live date is end of May and is at risk</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>MBA</t>
-  </si>
-  <si>
-    <t>MN</t>
-  </si>
-  <si>
-    <t>ME</t>
-  </si>
-  <si>
-    <t>IA</t>
-  </si>
-  <si>
-    <t>Ankit</t>
-  </si>
-  <si>
-    <t>Sif Unity, IA current backlog and future commitments</t>
-  </si>
-  <si>
-    <t>Sif Unity yearcoming up.</t>
-  </si>
-  <si>
     <t>Fred is involved in all calls</t>
   </si>
   <si>
     <t>ND</t>
   </si>
   <si>
+    <t>LOST</t>
+  </si>
+  <si>
     <t>End of support from June -26</t>
   </si>
   <si>
@@ -427,6 +458,12 @@
     <t>NY</t>
   </si>
   <si>
+    <t>Regina</t>
+  </si>
+  <si>
+    <t>No plan</t>
+  </si>
+  <si>
     <t>CA(esp)</t>
   </si>
   <si>
@@ -436,9 +473,6 @@
     <t>Prashu</t>
   </si>
   <si>
-    <t>Completed</t>
-  </si>
-  <si>
     <t>1 ticket ongoing communcaiton with customer. To be clarified with customers</t>
   </si>
   <si>
@@ -446,9 +480,6 @@
   </si>
   <si>
     <t>Prashu will lead customer calls from June</t>
-  </si>
-  <si>
-    <t>Debra</t>
   </si>
   <si>
     <t>MD(esp)</t>
@@ -506,13 +537,10 @@
     <t>Sivaprasad</t>
   </si>
   <si>
-    <t>Caron*</t>
-  </si>
-  <si>
     <t>WA</t>
   </si>
   <si>
-    <t>Dan*</t>
+    <t>Dan</t>
   </si>
   <si>
     <t>Dan leading the calls</t>
@@ -539,12 +567,18 @@
     <t>IL</t>
   </si>
   <si>
+    <t>Robyn</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prashu </t>
   </si>
   <si>
     <t>AK</t>
   </si>
   <si>
+    <t>Dan handles all customer intercations</t>
+  </si>
+  <si>
     <t>AK KT Confluence</t>
   </si>
   <si>
@@ -575,12 +609,18 @@
     <t>IN</t>
   </si>
   <si>
+    <t>Caron will start running the calls from Aug.</t>
+  </si>
+  <si>
     <t>https://powerschoolgroup.atlassian.net/wiki/spaces/SR/pages/68179034174/Indiana+State+Reporting+Product+Management+Knowledge+Transfer+Overview</t>
   </si>
   <si>
     <t>NE</t>
   </si>
   <si>
+    <t>KT not started</t>
+  </si>
+  <si>
     <t>CA</t>
   </si>
   <si>
@@ -590,9 +630,15 @@
     <t>CA Transition Document</t>
   </si>
   <si>
+    <t>Jason leading calls</t>
+  </si>
+  <si>
     <t>AL</t>
   </si>
   <si>
+    <t>Debra</t>
+  </si>
+  <si>
     <t>FL (SIS)</t>
   </si>
   <si>
@@ -603,6 +649,9 @@
   </si>
   <si>
     <t>Vette</t>
+  </si>
+  <si>
+    <t>Vette leads all meetings</t>
   </si>
   <si>
     <t>TN</t>
@@ -618,40 +667,15 @@
 </t>
   </si>
   <si>
-    <t>KT not started</t>
-  </si>
-  <si>
-    <t>Jason leading calls</t>
-  </si>
-  <si>
-    <t>Not planned</t>
-  </si>
-  <si>
-    <t>Shannita handles all customer intercations</t>
-  </si>
-  <si>
-    <t>Dan handles all customer intercations</t>
-  </si>
-  <si>
-    <t>Caron will start running the calls from Aug.</t>
-  </si>
-  <si>
-    <t>No plan</t>
-  </si>
-  <si>
-    <t>SIF Unity tickets created.
-Chhaya is part of all calls with customer and handling tickets.</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>Grooming</t>
   </si>
   <si>
     <t>Demos</t>
   </si>
   <si>
+    <t>New requirements/tickets</t>
+  </si>
+  <si>
     <t>Customer slides</t>
   </si>
   <si>
@@ -673,50 +697,20 @@
     <t>US PM Vacation/ Conference support</t>
   </si>
   <si>
-    <t>Robyn</t>
-  </si>
-  <si>
-    <t>Regina</t>
-  </si>
-  <si>
-    <t>Prisana Shaw</t>
-  </si>
-  <si>
-    <t>Jason</t>
-  </si>
-  <si>
-    <t>Caron</t>
-  </si>
-  <si>
-    <t>Anuj/ Jessica</t>
-  </si>
-  <si>
-    <t>Anuj /Turab</t>
-  </si>
-  <si>
-    <t>Anuj/Jessica</t>
-  </si>
-  <si>
-    <t>Dan</t>
-  </si>
-  <si>
-    <t>New requirements/tickets</t>
-  </si>
-  <si>
-    <t>LOST</t>
-  </si>
-  <si>
-    <t>Regina/Vette</t>
-  </si>
-  <si>
-    <t>Vette/Regina</t>
+    <t xml:space="preserve">Vette </t>
+  </si>
+  <si>
+    <t>Readiness Score - kt</t>
+  </si>
+  <si>
+    <t>State / Product Area</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -754,14 +748,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -780,8 +768,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -804,23 +798,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -865,10 +848,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1236,6 +1216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P69"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1306,7 +1287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -1326,41 +1307,41 @@
         <v>20</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="P2" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P3" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
@@ -1375,18 +1356,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -1395,79 +1376,79 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="3">
-        <v>100</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P7" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -1476,38 +1457,38 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P9" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>18</v>
@@ -1522,140 +1503,140 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3">
         <v>100</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P11" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12" s="3">
         <v>90</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P12" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>188</v>
+        <v>59</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="3">
         <v>100</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P13" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1664,61 +1645,61 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="D16" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17" s="3">
         <v>100</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="P17" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>19</v>
@@ -1727,21 +1708,21 @@
         <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P18" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>189</v>
+        <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>19</v>
@@ -1750,141 +1731,141 @@
         <v>100</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P19" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P20" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21" s="3">
         <v>100</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="P21" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
@@ -1893,56 +1874,56 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E25" s="3">
         <v>100</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>173</v>
+        <v>90</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>187</v>
+        <v>93</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>19</v>
@@ -1951,24 +1932,24 @@
         <v>100</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P26" s="4">
         <v>46185</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27" s="3">
         <v>100</v>
@@ -1977,18 +1958,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28" s="3">
         <v>100</v>
@@ -1997,18 +1978,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29" s="3">
         <v>100</v>
@@ -2017,121 +1998,121 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E30" s="3">
         <v>100</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="P30" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E31" s="3">
         <v>0</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="P31" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="P32" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E33" s="3">
         <v>100</v>
@@ -2140,16 +2121,16 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E34" s="3">
         <v>0</v>
@@ -2158,181 +2139,181 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="P35" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E36" s="3">
         <v>100</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="P36" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E37" s="3">
         <v>100</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="P37" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E38" s="3">
         <v>100</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="P38" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E39" s="3">
         <v>100</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="P39" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D40" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E40" s="3">
         <v>100</v>
@@ -2341,53 +2322,53 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41" s="3">
         <v>100</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="P41" s="4">
         <v>46206</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2396,18 +2377,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
@@ -2416,36 +2397,36 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="11" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="P44" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -2454,18 +2435,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E46" s="3">
         <v>0</v>
@@ -2474,82 +2455,82 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="P47" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>187</v>
+        <v>93</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E48" s="3">
         <v>100</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P48" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E49" s="3">
         <v>100</v>
@@ -2558,22 +2539,22 @@
         <v>46174</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="P49" s="4">
         <v>46387</v>
@@ -2581,16 +2562,16 @@
     </row>
     <row r="50" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E50" s="3">
         <v>100</v>
@@ -2599,150 +2580,150 @@
         <v>46174</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P50" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E51" s="3">
+        <v>100</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D51" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E51" s="3">
-        <v>100</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D53" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E53" s="3">
         <v>100</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="P53" s="4"/>
     </row>
-    <row r="54" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E54" s="15">
         <v>100</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="P54" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E55" s="15">
         <v>100</v>
@@ -2751,18 +2732,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E56" s="15">
         <v>100</v>
@@ -2771,18 +2752,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E57" s="15">
         <v>100</v>
@@ -2791,18 +2772,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E58" s="15">
         <v>100</v>
@@ -2811,18 +2792,18 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E59" s="15">
         <v>100</v>
@@ -2831,74 +2812,74 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D60" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E60" s="15">
         <v>100</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="P60" s="4"/>
     </row>
-    <row r="61" spans="1:16" ht="144" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" ht="144" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="P61" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -2910,48 +2891,48 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E63" s="3">
         <v>100</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="P63" s="4">
         <v>46387</v>
@@ -2959,198 +2940,204 @@
     </row>
     <row r="64" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E64" s="3">
         <v>80</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P64" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="P65" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E66" s="3">
         <v>90</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="P66" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E67" s="3">
         <v>90</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="P67" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E68" s="3">
         <v>80</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="P68" s="4">
         <v>46387</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P69" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}"/>
+  <autoFilter ref="A1:P69" xr:uid="{21C61107-A291-4A2B-BB36-6DBA20B0522C}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Smitha"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="J54" r:id="rId1" xr:uid="{5DBA3A74-260E-4C5A-B9BA-696E7347EBA4}"/>
     <hyperlink ref="J60" r:id="rId2" xr:uid="{2A438ECF-BCA9-41C5-8312-3C3516217E53}"/>
@@ -3171,11 +3158,12 @@
     <col min="3" max="3" width="11.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="19" style="11" customWidth="1"/>
     <col min="5" max="5" width="10.5546875" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -3187,39 +3175,39 @@
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="H1" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="N1" s="16" t="s">
+      <c r="F1" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="G1" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="16"/>
+      <c r="H1" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="P1" s="8"/>
     </row>
     <row r="2" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -3234,90 +3222,90 @@
       <c r="D2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="3">
-        <v>100</v>
-      </c>
-      <c r="F2">
+      <c r="E2" s="16">
+        <v>100</v>
+      </c>
+      <c r="F2" s="11">
         <v>30</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="11">
         <v>30</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="H2" s="11">
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
         <v>30</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="11">
         <v>30</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="11">
         <v>50</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="11">
         <v>30</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
+      <c r="M2" s="11">
+        <v>0</v>
+      </c>
+      <c r="N2" s="11">
+        <v>0</v>
+      </c>
+      <c r="O2" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="3">
-        <v>100</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E3" s="16">
+        <v>100</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
@@ -3325,272 +3313,272 @@
       <c r="D4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="3">
-        <v>100</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>22</v>
+      <c r="E4" s="16">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3">
-        <v>100</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E5" s="16">
+        <v>100</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="3">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
+        <v>24</v>
+      </c>
+      <c r="E6" s="16">
+        <v>100</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0</v>
+      </c>
+      <c r="J6" s="11">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0</v>
+      </c>
+      <c r="L6" s="11">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11">
+        <v>0</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0</v>
+      </c>
+      <c r="O6" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="3">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
+        <v>38</v>
+      </c>
+      <c r="E7" s="16">
+        <v>100</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0</v>
+      </c>
+      <c r="K7" s="11">
+        <v>0</v>
+      </c>
+      <c r="L7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0</v>
+      </c>
+      <c r="O7" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="3">
-        <v>100</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E8" s="16">
+        <v>100</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="3">
-        <v>100</v>
-      </c>
-      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="E9" s="16">
+        <v>100</v>
+      </c>
+      <c r="F9" s="11">
         <v>80</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="11">
         <v>50</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
+      <c r="H9" s="11">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0</v>
+      </c>
+      <c r="J9" s="11">
         <v>20</v>
       </c>
-      <c r="K9">
-        <v>100</v>
-      </c>
-      <c r="L9">
+      <c r="K9" s="11">
+        <v>100</v>
+      </c>
+      <c r="L9" s="11">
         <v>80</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="11">
         <v>50</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
+      <c r="N9" s="11">
+        <v>0</v>
+      </c>
+      <c r="O9" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>18</v>
@@ -3598,2609 +3586,2612 @@
       <c r="D10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="3">
-        <v>100</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>22</v>
+      <c r="E10" s="16">
+        <v>100</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" s="3">
-        <v>100</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="E11" s="16">
+        <v>100</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12" s="3">
         <v>90</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="11">
         <v>80</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="11">
         <v>80</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="11">
         <v>50</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="11">
+        <v>0</v>
+      </c>
+      <c r="J12" s="11">
+        <v>30</v>
+      </c>
+      <c r="K12" s="11">
+        <v>100</v>
+      </c>
+      <c r="L12" s="11">
+        <v>100</v>
+      </c>
+      <c r="M12" s="11">
+        <v>30</v>
+      </c>
+      <c r="N12" s="11">
         <v>20</v>
       </c>
-      <c r="J12">
-        <v>50</v>
-      </c>
-      <c r="K12">
-        <v>100</v>
-      </c>
-      <c r="L12">
-        <v>100</v>
-      </c>
-      <c r="M12">
-        <v>50</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
+      <c r="O12" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>188</v>
+        <v>59</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="3">
-        <v>100</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E13" s="16">
+        <v>100</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="3">
-        <v>100</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E15" s="16">
+        <v>100</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="D16" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="3">
-        <v>100</v>
-      </c>
-      <c r="F17">
+        <v>24</v>
+      </c>
+      <c r="E17" s="16">
+        <v>100</v>
+      </c>
+      <c r="F17" s="11">
         <v>80</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="11">
         <v>50</v>
       </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
+      <c r="H17" s="11">
+        <v>0</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0</v>
+      </c>
+      <c r="J17" s="11">
         <v>20</v>
       </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
-      <c r="L17">
+      <c r="K17" s="11">
+        <v>100</v>
+      </c>
+      <c r="L17" s="11">
         <v>80</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="11">
         <v>50</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
+      <c r="N17" s="11">
+        <v>0</v>
+      </c>
+      <c r="O17" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="16">
         <v>100</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>189</v>
+        <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="3">
-        <v>100</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M19" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>22</v>
+      <c r="E19" s="16">
+        <v>100</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20">
-        <v>100</v>
-      </c>
-      <c r="G20">
-        <v>100</v>
-      </c>
-      <c r="H20">
-        <v>100</v>
-      </c>
-      <c r="I20">
-        <v>100</v>
-      </c>
-      <c r="J20">
-        <v>90</v>
-      </c>
-      <c r="K20">
-        <v>100</v>
-      </c>
-      <c r="L20">
-        <v>100</v>
-      </c>
-      <c r="M20">
-        <v>75</v>
-      </c>
-      <c r="N20">
+      <c r="F20" s="11">
+        <v>100</v>
+      </c>
+      <c r="G20" s="11">
+        <v>100</v>
+      </c>
+      <c r="H20" s="11">
+        <v>100</v>
+      </c>
+      <c r="I20" s="11">
+        <v>100</v>
+      </c>
+      <c r="J20" s="11">
+        <v>100</v>
+      </c>
+      <c r="K20" s="11">
+        <v>100</v>
+      </c>
+      <c r="L20" s="11">
+        <v>100</v>
+      </c>
+      <c r="M20" s="11">
+        <v>100</v>
+      </c>
+      <c r="N20" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="3">
-        <v>100</v>
-      </c>
-      <c r="F21">
+        <v>24</v>
+      </c>
+      <c r="E21" s="16">
+        <v>100</v>
+      </c>
+      <c r="F21" s="11">
         <v>80</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="11">
         <v>50</v>
       </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
+      <c r="H21" s="11">
+        <v>0</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0</v>
+      </c>
+      <c r="J21" s="11">
         <v>20</v>
       </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
-      <c r="L21">
+      <c r="K21" s="11">
+        <v>100</v>
+      </c>
+      <c r="L21" s="11">
         <v>80</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="11">
         <v>50</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
+      <c r="N21" s="11">
+        <v>0</v>
+      </c>
+      <c r="O21" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" s="3">
-        <v>100</v>
-      </c>
-      <c r="F22">
-        <v>100</v>
-      </c>
-      <c r="G22">
         <v>50</v>
       </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
+      <c r="E22" s="16">
+        <v>100</v>
+      </c>
+      <c r="F22" s="11">
+        <v>100</v>
+      </c>
+      <c r="G22" s="11">
+        <v>50</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0</v>
+      </c>
+      <c r="J22" s="11">
+        <v>0</v>
+      </c>
+      <c r="K22" s="11">
+        <v>0</v>
+      </c>
+      <c r="L22" s="11">
+        <v>100</v>
+      </c>
+      <c r="M22" s="11">
+        <v>0</v>
+      </c>
+      <c r="N22" s="11">
+        <v>0</v>
+      </c>
+      <c r="O22" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="3">
-        <v>100</v>
-      </c>
-      <c r="F24" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" t="s">
-        <v>22</v>
-      </c>
-      <c r="K24" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" t="s">
-        <v>22</v>
-      </c>
-      <c r="M24" t="s">
-        <v>22</v>
-      </c>
-      <c r="N24" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="E24" s="16">
+        <v>100</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="3">
-        <v>100</v>
-      </c>
-      <c r="F25">
-        <v>100</v>
-      </c>
-      <c r="G25">
         <v>50</v>
       </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>100</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
+      <c r="E25" s="16">
+        <v>100</v>
+      </c>
+      <c r="F25" s="11">
+        <v>100</v>
+      </c>
+      <c r="G25" s="11">
+        <v>50</v>
+      </c>
+      <c r="H25" s="11">
+        <v>0</v>
+      </c>
+      <c r="I25" s="11">
+        <v>0</v>
+      </c>
+      <c r="J25" s="11">
+        <v>0</v>
+      </c>
+      <c r="K25" s="11">
+        <v>0</v>
+      </c>
+      <c r="L25" s="11">
+        <v>100</v>
+      </c>
+      <c r="M25" s="11">
+        <v>0</v>
+      </c>
+      <c r="N25" s="11">
+        <v>0</v>
+      </c>
+      <c r="O25" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>187</v>
+        <v>93</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="3">
-        <v>100</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K26" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L26" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M26" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" s="17" t="s">
-        <v>22</v>
+      <c r="E26" s="16">
+        <v>100</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="3">
+        <v>24</v>
+      </c>
+      <c r="E27" s="16">
         <v>100</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="3">
+        <v>24</v>
+      </c>
+      <c r="E28" s="16">
         <v>100</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="3">
+        <v>24</v>
+      </c>
+      <c r="E29" s="16">
         <v>100</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="3">
-        <v>100</v>
-      </c>
-      <c r="F30">
+        <v>24</v>
+      </c>
+      <c r="E30" s="16">
+        <v>100</v>
+      </c>
+      <c r="F30" s="11">
         <v>80</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="11">
         <v>50</v>
       </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>100</v>
-      </c>
-      <c r="L30">
+      <c r="H30" s="11">
+        <v>0</v>
+      </c>
+      <c r="I30" s="11">
+        <v>0</v>
+      </c>
+      <c r="J30" s="11">
+        <v>0</v>
+      </c>
+      <c r="K30" s="11">
+        <v>100</v>
+      </c>
+      <c r="L30" s="11">
         <v>80</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="11">
         <v>50</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
+      <c r="N30" s="11">
+        <v>0</v>
+      </c>
+      <c r="O30" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E31" s="3">
         <v>0</v>
       </c>
-      <c r="F31">
-        <v>100</v>
-      </c>
-      <c r="G31">
-        <v>100</v>
-      </c>
-      <c r="H31">
-        <v>100</v>
-      </c>
-      <c r="I31">
-        <v>100</v>
-      </c>
-      <c r="J31">
-        <v>100</v>
-      </c>
-      <c r="K31">
-        <v>100</v>
-      </c>
-      <c r="L31">
-        <v>100</v>
-      </c>
-      <c r="M31">
-        <v>100</v>
-      </c>
-      <c r="N31">
+      <c r="F31" s="11">
+        <v>100</v>
+      </c>
+      <c r="G31" s="11">
+        <v>100</v>
+      </c>
+      <c r="H31" s="11">
+        <v>100</v>
+      </c>
+      <c r="I31" s="11">
+        <v>100</v>
+      </c>
+      <c r="J31" s="11">
+        <v>100</v>
+      </c>
+      <c r="K31" s="11">
+        <v>100</v>
+      </c>
+      <c r="L31" s="11">
+        <v>100</v>
+      </c>
+      <c r="M31" s="11">
+        <v>100</v>
+      </c>
+      <c r="N31" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E33" s="3">
-        <v>100</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
+        <v>38</v>
+      </c>
+      <c r="E33" s="16">
+        <v>100</v>
+      </c>
+      <c r="F33" s="11">
+        <v>0</v>
+      </c>
+      <c r="G33" s="11">
+        <v>0</v>
+      </c>
+      <c r="H33" s="11">
+        <v>0</v>
+      </c>
+      <c r="I33" s="11">
+        <v>0</v>
+      </c>
+      <c r="J33" s="11">
+        <v>0</v>
+      </c>
+      <c r="K33" s="11">
+        <v>0</v>
+      </c>
+      <c r="L33" s="11">
+        <v>0</v>
+      </c>
+      <c r="M33" s="11">
+        <v>0</v>
+      </c>
+      <c r="N33" s="11">
+        <v>0</v>
+      </c>
+      <c r="O33" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E34" s="3">
         <v>0</v>
       </c>
-      <c r="F34">
-        <v>100</v>
-      </c>
-      <c r="G34">
-        <v>100</v>
-      </c>
-      <c r="H34">
-        <v>100</v>
-      </c>
-      <c r="I34">
-        <v>100</v>
-      </c>
-      <c r="J34">
-        <v>100</v>
-      </c>
-      <c r="K34">
-        <v>100</v>
-      </c>
-      <c r="L34">
-        <v>100</v>
-      </c>
-      <c r="M34">
-        <v>100</v>
-      </c>
-      <c r="N34">
+      <c r="F34" s="11">
+        <v>100</v>
+      </c>
+      <c r="G34" s="11">
+        <v>100</v>
+      </c>
+      <c r="H34" s="11">
+        <v>100</v>
+      </c>
+      <c r="I34" s="11">
+        <v>100</v>
+      </c>
+      <c r="J34" s="11">
+        <v>100</v>
+      </c>
+      <c r="K34" s="11">
+        <v>100</v>
+      </c>
+      <c r="L34" s="11">
+        <v>100</v>
+      </c>
+      <c r="M34" s="11">
+        <v>100</v>
+      </c>
+      <c r="N34" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
       </c>
-      <c r="F35">
-        <v>100</v>
-      </c>
-      <c r="G35">
-        <v>100</v>
-      </c>
-      <c r="H35">
-        <v>100</v>
-      </c>
-      <c r="I35">
-        <v>100</v>
-      </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
-      <c r="K35">
-        <v>100</v>
-      </c>
-      <c r="L35">
-        <v>100</v>
-      </c>
-      <c r="M35">
-        <v>100</v>
-      </c>
-      <c r="N35">
-        <v>100</v>
-      </c>
-      <c r="O35">
+      <c r="F35" s="11">
+        <v>100</v>
+      </c>
+      <c r="G35" s="11">
+        <v>100</v>
+      </c>
+      <c r="H35" s="11">
+        <v>100</v>
+      </c>
+      <c r="I35" s="11">
+        <v>100</v>
+      </c>
+      <c r="J35" s="11">
+        <v>100</v>
+      </c>
+      <c r="K35" s="11">
+        <v>100</v>
+      </c>
+      <c r="L35" s="11">
+        <v>100</v>
+      </c>
+      <c r="M35" s="11">
+        <v>100</v>
+      </c>
+      <c r="N35" s="11">
+        <v>100</v>
+      </c>
+      <c r="O35" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E36" s="3">
-        <v>100</v>
-      </c>
-      <c r="F36">
-        <v>100</v>
-      </c>
-      <c r="G36">
-        <v>100</v>
-      </c>
-      <c r="H36">
-        <v>100</v>
-      </c>
-      <c r="I36">
-        <v>100</v>
-      </c>
-      <c r="J36">
-        <v>100</v>
-      </c>
-      <c r="K36">
-        <v>100</v>
-      </c>
-      <c r="L36">
-        <v>100</v>
-      </c>
-      <c r="M36">
-        <v>100</v>
-      </c>
-      <c r="N36">
+        <v>50</v>
+      </c>
+      <c r="E36" s="16">
+        <v>100</v>
+      </c>
+      <c r="F36" s="11">
+        <v>100</v>
+      </c>
+      <c r="G36" s="11">
+        <v>100</v>
+      </c>
+      <c r="H36" s="11">
+        <v>100</v>
+      </c>
+      <c r="I36" s="11">
+        <v>100</v>
+      </c>
+      <c r="J36" s="11">
+        <v>100</v>
+      </c>
+      <c r="K36" s="11">
+        <v>100</v>
+      </c>
+      <c r="L36" s="11">
+        <v>100</v>
+      </c>
+      <c r="M36" s="11">
+        <v>100</v>
+      </c>
+      <c r="N36" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E37" s="3">
-        <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" t="s">
-        <v>22</v>
-      </c>
-      <c r="K37" t="s">
-        <v>22</v>
-      </c>
-      <c r="L37" t="s">
-        <v>22</v>
-      </c>
-      <c r="M37" t="s">
-        <v>22</v>
-      </c>
-      <c r="N37" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="E37" s="16">
+        <v>100</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N37" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E38" s="3">
-        <v>100</v>
-      </c>
-      <c r="F38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G38" t="s">
-        <v>22</v>
-      </c>
-      <c r="H38" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" t="s">
-        <v>22</v>
-      </c>
-      <c r="J38" t="s">
-        <v>22</v>
-      </c>
-      <c r="K38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L38" t="s">
-        <v>22</v>
-      </c>
-      <c r="M38" t="s">
-        <v>22</v>
-      </c>
-      <c r="N38" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="E38" s="16">
+        <v>100</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E39" s="3">
-        <v>100</v>
-      </c>
-      <c r="F39">
-        <v>100</v>
-      </c>
-      <c r="G39">
-        <v>100</v>
-      </c>
-      <c r="H39">
-        <v>100</v>
-      </c>
-      <c r="I39">
-        <v>100</v>
-      </c>
-      <c r="J39">
-        <v>100</v>
-      </c>
-      <c r="K39">
-        <v>100</v>
-      </c>
-      <c r="L39">
-        <v>100</v>
-      </c>
-      <c r="M39">
-        <v>100</v>
-      </c>
-      <c r="N39">
+        <v>50</v>
+      </c>
+      <c r="E39" s="16">
+        <v>100</v>
+      </c>
+      <c r="F39" s="11">
+        <v>100</v>
+      </c>
+      <c r="G39" s="11">
+        <v>100</v>
+      </c>
+      <c r="H39" s="11">
+        <v>100</v>
+      </c>
+      <c r="I39" s="11">
+        <v>100</v>
+      </c>
+      <c r="J39" s="11">
+        <v>100</v>
+      </c>
+      <c r="K39" s="11">
+        <v>100</v>
+      </c>
+      <c r="L39" s="11">
+        <v>100</v>
+      </c>
+      <c r="M39" s="11">
+        <v>100</v>
+      </c>
+      <c r="N39" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="D40" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E40" s="3">
-        <v>100</v>
-      </c>
-      <c r="F40">
-        <v>100</v>
-      </c>
-      <c r="G40">
-        <v>100</v>
-      </c>
-      <c r="H40">
-        <v>100</v>
-      </c>
-      <c r="I40">
-        <v>100</v>
-      </c>
-      <c r="J40">
-        <v>100</v>
-      </c>
-      <c r="K40">
-        <v>100</v>
-      </c>
-      <c r="L40">
-        <v>100</v>
-      </c>
-      <c r="M40">
-        <v>100</v>
-      </c>
-      <c r="N40">
+        <v>50</v>
+      </c>
+      <c r="E40" s="16">
+        <v>100</v>
+      </c>
+      <c r="F40" s="11">
+        <v>100</v>
+      </c>
+      <c r="G40" s="11">
+        <v>100</v>
+      </c>
+      <c r="H40" s="11">
+        <v>100</v>
+      </c>
+      <c r="I40" s="11">
+        <v>100</v>
+      </c>
+      <c r="J40" s="11">
+        <v>100</v>
+      </c>
+      <c r="K40" s="11">
+        <v>100</v>
+      </c>
+      <c r="L40" s="11">
+        <v>100</v>
+      </c>
+      <c r="M40" s="11">
+        <v>100</v>
+      </c>
+      <c r="N40" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" s="3">
-        <v>100</v>
-      </c>
-      <c r="F41" t="s">
-        <v>22</v>
-      </c>
-      <c r="G41" t="s">
-        <v>22</v>
-      </c>
-      <c r="H41" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" t="s">
-        <v>22</v>
-      </c>
-      <c r="J41" t="s">
-        <v>22</v>
-      </c>
-      <c r="K41" t="s">
-        <v>22</v>
-      </c>
-      <c r="L41" t="s">
-        <v>22</v>
-      </c>
-      <c r="M41" t="s">
-        <v>22</v>
-      </c>
-      <c r="N41" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E41" s="16">
+        <v>100</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
-      <c r="F42">
-        <v>100</v>
-      </c>
-      <c r="G42">
-        <v>100</v>
-      </c>
-      <c r="H42">
-        <v>100</v>
-      </c>
-      <c r="I42">
-        <v>100</v>
-      </c>
-      <c r="J42">
-        <v>100</v>
-      </c>
-      <c r="K42">
-        <v>100</v>
-      </c>
-      <c r="L42">
-        <v>100</v>
-      </c>
-      <c r="M42">
-        <v>100</v>
-      </c>
-      <c r="N42">
+      <c r="F42" s="11">
+        <v>100</v>
+      </c>
+      <c r="G42" s="11">
+        <v>100</v>
+      </c>
+      <c r="H42" s="11">
+        <v>100</v>
+      </c>
+      <c r="I42" s="11">
+        <v>100</v>
+      </c>
+      <c r="J42" s="11">
+        <v>100</v>
+      </c>
+      <c r="K42" s="11">
+        <v>100</v>
+      </c>
+      <c r="L42" s="11">
+        <v>100</v>
+      </c>
+      <c r="M42" s="11">
+        <v>100</v>
+      </c>
+      <c r="N42" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E43" s="3">
-        <v>100</v>
-      </c>
-      <c r="F43">
-        <v>100</v>
-      </c>
-      <c r="G43">
-        <v>100</v>
-      </c>
-      <c r="H43">
-        <v>100</v>
-      </c>
-      <c r="I43">
-        <v>100</v>
-      </c>
-      <c r="J43">
-        <v>100</v>
-      </c>
-      <c r="K43">
-        <v>100</v>
-      </c>
-      <c r="L43">
-        <v>100</v>
-      </c>
-      <c r="M43">
-        <v>100</v>
-      </c>
-      <c r="N43">
+        <v>78</v>
+      </c>
+      <c r="E43" s="16">
+        <v>100</v>
+      </c>
+      <c r="F43" s="11">
+        <v>100</v>
+      </c>
+      <c r="G43" s="11">
+        <v>100</v>
+      </c>
+      <c r="H43" s="11">
+        <v>100</v>
+      </c>
+      <c r="I43" s="11">
+        <v>100</v>
+      </c>
+      <c r="J43" s="11">
+        <v>100</v>
+      </c>
+      <c r="K43" s="11">
+        <v>100</v>
+      </c>
+      <c r="L43" s="11">
+        <v>100</v>
+      </c>
+      <c r="M43" s="11">
+        <v>100</v>
+      </c>
+      <c r="N43" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="11" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
-      <c r="F45">
-        <v>100</v>
-      </c>
-      <c r="G45">
-        <v>100</v>
-      </c>
-      <c r="H45">
-        <v>100</v>
-      </c>
-      <c r="I45">
-        <v>100</v>
-      </c>
-      <c r="J45">
-        <v>100</v>
-      </c>
-      <c r="K45">
-        <v>100</v>
-      </c>
-      <c r="L45">
-        <v>100</v>
-      </c>
-      <c r="M45">
-        <v>100</v>
-      </c>
-      <c r="N45">
+      <c r="F45" s="11">
+        <v>100</v>
+      </c>
+      <c r="G45" s="11">
+        <v>100</v>
+      </c>
+      <c r="H45" s="11">
+        <v>100</v>
+      </c>
+      <c r="I45" s="11">
+        <v>100</v>
+      </c>
+      <c r="J45" s="11">
+        <v>100</v>
+      </c>
+      <c r="K45" s="11">
+        <v>100</v>
+      </c>
+      <c r="L45" s="11">
+        <v>100</v>
+      </c>
+      <c r="M45" s="11">
+        <v>100</v>
+      </c>
+      <c r="N45" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E46" s="3">
         <v>0</v>
       </c>
-      <c r="F46">
-        <v>100</v>
-      </c>
-      <c r="G46">
-        <v>100</v>
-      </c>
-      <c r="H46">
-        <v>100</v>
-      </c>
-      <c r="I46">
-        <v>100</v>
-      </c>
-      <c r="J46">
-        <v>100</v>
-      </c>
-      <c r="K46">
-        <v>100</v>
-      </c>
-      <c r="L46">
-        <v>100</v>
-      </c>
-      <c r="M46">
-        <v>100</v>
-      </c>
-      <c r="N46">
+      <c r="F46" s="11">
+        <v>100</v>
+      </c>
+      <c r="G46" s="11">
+        <v>100</v>
+      </c>
+      <c r="H46" s="11">
+        <v>100</v>
+      </c>
+      <c r="I46" s="11">
+        <v>100</v>
+      </c>
+      <c r="J46" s="11">
+        <v>100</v>
+      </c>
+      <c r="K46" s="11">
+        <v>100</v>
+      </c>
+      <c r="L46" s="11">
+        <v>100</v>
+      </c>
+      <c r="M46" s="11">
+        <v>100</v>
+      </c>
+      <c r="N46" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>187</v>
+        <v>93</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E48" s="3">
-        <v>100</v>
-      </c>
-      <c r="F48">
-        <v>100</v>
-      </c>
-      <c r="G48">
-        <v>100</v>
-      </c>
-      <c r="H48">
-        <v>100</v>
-      </c>
-      <c r="I48">
-        <v>100</v>
-      </c>
-      <c r="J48">
-        <v>100</v>
-      </c>
-      <c r="K48">
+        <v>38</v>
+      </c>
+      <c r="E48" s="16">
+        <v>100</v>
+      </c>
+      <c r="F48" s="11">
+        <v>100</v>
+      </c>
+      <c r="G48" s="11">
+        <v>100</v>
+      </c>
+      <c r="H48" s="11">
+        <v>100</v>
+      </c>
+      <c r="I48" s="11">
+        <v>100</v>
+      </c>
+      <c r="J48" s="11">
+        <v>100</v>
+      </c>
+      <c r="K48" s="11">
         <v>50</v>
       </c>
-      <c r="L48">
-        <v>100</v>
-      </c>
-      <c r="M48">
+      <c r="L48" s="11">
+        <v>100</v>
+      </c>
+      <c r="M48" s="11">
         <v>50</v>
       </c>
-      <c r="N48">
+      <c r="N48" s="11">
         <v>80</v>
       </c>
-      <c r="O48">
+      <c r="O48" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E49" s="3">
-        <v>100</v>
-      </c>
-      <c r="F49">
-        <v>100</v>
-      </c>
-      <c r="G49">
-        <v>100</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
+        <v>50</v>
+      </c>
+      <c r="E49" s="16">
+        <v>100</v>
+      </c>
+      <c r="F49" s="11">
+        <v>100</v>
+      </c>
+      <c r="G49" s="11">
+        <v>100</v>
+      </c>
+      <c r="H49" s="11">
+        <v>0</v>
+      </c>
+      <c r="I49" s="11">
+        <v>0</v>
+      </c>
+      <c r="J49" s="11">
         <v>20</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="11">
         <v>50</v>
       </c>
-      <c r="L49">
+      <c r="L49" s="11">
         <v>50</v>
       </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
+      <c r="M49" s="11">
+        <v>0</v>
+      </c>
+      <c r="N49" s="11">
+        <v>0</v>
+      </c>
+      <c r="O49" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E50" s="3">
-        <v>100</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="G50">
-        <v>100</v>
-      </c>
-      <c r="H50">
+        <v>50</v>
+      </c>
+      <c r="E50" s="16">
+        <v>100</v>
+      </c>
+      <c r="F50" s="11">
+        <v>0</v>
+      </c>
+      <c r="G50" s="11">
+        <v>100</v>
+      </c>
+      <c r="H50" s="11">
         <v>20</v>
       </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
+      <c r="I50" s="11">
+        <v>0</v>
+      </c>
+      <c r="J50" s="11">
+        <v>0</v>
+      </c>
+      <c r="K50" s="11">
         <v>30</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="11">
         <v>50</v>
       </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
+      <c r="M50" s="11">
+        <v>0</v>
+      </c>
+      <c r="N50" s="11">
+        <v>0</v>
+      </c>
+      <c r="O50" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E51" s="3">
-        <v>100</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
+        <v>50</v>
+      </c>
+      <c r="E51" s="16">
+        <v>100</v>
+      </c>
+      <c r="F51" s="11">
+        <v>0</v>
+      </c>
+      <c r="G51" s="11">
+        <v>0</v>
+      </c>
+      <c r="H51" s="11">
+        <v>0</v>
+      </c>
+      <c r="I51" s="11">
+        <v>0</v>
+      </c>
+      <c r="J51" s="11">
+        <v>0</v>
+      </c>
+      <c r="K51" s="11">
+        <v>0</v>
+      </c>
+      <c r="L51" s="11">
+        <v>0</v>
+      </c>
+      <c r="M51" s="11">
+        <v>0</v>
+      </c>
+      <c r="N51" s="11">
+        <v>0</v>
+      </c>
+      <c r="O51" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
-      <c r="F52">
-        <v>100</v>
-      </c>
-      <c r="G52">
-        <v>100</v>
-      </c>
-      <c r="H52">
-        <v>100</v>
-      </c>
-      <c r="I52">
-        <v>100</v>
-      </c>
-      <c r="J52">
-        <v>100</v>
-      </c>
-      <c r="K52">
-        <v>100</v>
-      </c>
-      <c r="L52">
-        <v>100</v>
-      </c>
-      <c r="M52">
-        <v>100</v>
-      </c>
-      <c r="N52">
-        <v>100</v>
-      </c>
-      <c r="O52">
+      <c r="F52" s="11">
+        <v>100</v>
+      </c>
+      <c r="G52" s="11">
+        <v>100</v>
+      </c>
+      <c r="H52" s="11">
+        <v>100</v>
+      </c>
+      <c r="I52" s="11">
+        <v>100</v>
+      </c>
+      <c r="J52" s="11">
+        <v>100</v>
+      </c>
+      <c r="K52" s="11">
+        <v>100</v>
+      </c>
+      <c r="L52" s="11">
+        <v>100</v>
+      </c>
+      <c r="M52" s="11">
+        <v>100</v>
+      </c>
+      <c r="N52" s="11">
+        <v>100</v>
+      </c>
+      <c r="O52" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D53" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E53" s="3">
-        <v>100</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
+        <v>50</v>
+      </c>
+      <c r="E53" s="16">
+        <v>100</v>
+      </c>
+      <c r="F53" s="11">
+        <v>0</v>
+      </c>
+      <c r="G53" s="11">
+        <v>0</v>
+      </c>
+      <c r="H53" s="11">
+        <v>0</v>
+      </c>
+      <c r="I53" s="11">
+        <v>0</v>
+      </c>
+      <c r="J53" s="11">
+        <v>0</v>
+      </c>
+      <c r="K53" s="11">
+        <v>0</v>
+      </c>
+      <c r="L53" s="11">
+        <v>0</v>
+      </c>
+      <c r="M53" s="11">
+        <v>0</v>
+      </c>
+      <c r="N53" s="11">
+        <v>0</v>
+      </c>
+      <c r="O53" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E54" s="15">
-        <v>100</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54">
+        <v>50</v>
+      </c>
+      <c r="E54" s="16">
+        <v>100</v>
+      </c>
+      <c r="F54" s="11">
+        <v>0</v>
+      </c>
+      <c r="G54" s="11">
+        <v>0</v>
+      </c>
+      <c r="H54" s="11">
+        <v>0</v>
+      </c>
+      <c r="I54" s="11">
+        <v>0</v>
+      </c>
+      <c r="J54" s="11">
+        <v>0</v>
+      </c>
+      <c r="K54" s="11">
+        <v>0</v>
+      </c>
+      <c r="L54" s="11">
+        <v>0</v>
+      </c>
+      <c r="M54" s="11">
+        <v>0</v>
+      </c>
+      <c r="N54" s="11">
+        <v>0</v>
+      </c>
+      <c r="O54" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" s="15">
-        <v>100</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H55" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I55" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J55" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K55" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L55" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M55" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N55" s="17" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E55" s="16">
+        <v>100</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" s="15">
-        <v>100</v>
-      </c>
-      <c r="F56" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G56" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I56" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J56" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K56" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L56" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M56" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N56" s="17" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E56" s="16">
+        <v>100</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" s="15">
-        <v>100</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I57" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J57" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K57" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L57" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M57" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N57" s="17" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E57" s="16">
+        <v>100</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" s="15">
-        <v>100</v>
-      </c>
-      <c r="F58" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G58" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H58" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I58" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K58" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L58" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M58" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N58" s="17" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E58" s="16">
+        <v>100</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E59" s="15">
-        <v>100</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G59" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H59" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I59" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J59" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="K59" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L59" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M59" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N59" s="17" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E59" s="16">
+        <v>100</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D60" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E60" s="15">
-        <v>100</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <v>0</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
+        <v>50</v>
+      </c>
+      <c r="E60" s="16">
+        <v>100</v>
+      </c>
+      <c r="F60" s="11">
+        <v>0</v>
+      </c>
+      <c r="G60" s="11">
+        <v>0</v>
+      </c>
+      <c r="H60" s="11">
+        <v>0</v>
+      </c>
+      <c r="I60" s="11">
+        <v>0</v>
+      </c>
+      <c r="J60" s="11">
+        <v>0</v>
+      </c>
+      <c r="K60" s="11">
+        <v>0</v>
+      </c>
+      <c r="L60" s="11">
+        <v>0</v>
+      </c>
+      <c r="M60" s="11">
+        <v>0</v>
+      </c>
+      <c r="N60" s="11">
+        <v>0</v>
+      </c>
+      <c r="O60" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E61" s="3">
-        <v>100</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
+        <v>38</v>
+      </c>
+      <c r="E61" s="16">
+        <v>100</v>
+      </c>
+      <c r="F61" s="11">
+        <v>0</v>
+      </c>
+      <c r="G61" s="11">
+        <v>0</v>
+      </c>
+      <c r="H61" s="11">
+        <v>0</v>
+      </c>
+      <c r="I61" s="11">
+        <v>0</v>
+      </c>
+      <c r="J61" s="11">
+        <v>0</v>
+      </c>
+      <c r="K61" s="11">
+        <v>0</v>
+      </c>
+      <c r="L61" s="11">
+        <v>0</v>
+      </c>
+      <c r="M61" s="11">
+        <v>0</v>
+      </c>
+      <c r="N61" s="11">
+        <v>0</v>
+      </c>
+      <c r="O61" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
-      <c r="F62">
-        <v>100</v>
-      </c>
-      <c r="G62">
-        <v>100</v>
-      </c>
-      <c r="H62">
-        <v>100</v>
-      </c>
-      <c r="I62">
-        <v>100</v>
-      </c>
-      <c r="J62">
-        <v>100</v>
-      </c>
-      <c r="K62">
-        <v>100</v>
-      </c>
-      <c r="L62">
-        <v>100</v>
-      </c>
-      <c r="M62">
-        <v>100</v>
-      </c>
-      <c r="N62">
+      <c r="F62" s="11">
+        <v>100</v>
+      </c>
+      <c r="G62" s="11">
+        <v>100</v>
+      </c>
+      <c r="H62" s="11">
+        <v>100</v>
+      </c>
+      <c r="I62" s="11">
+        <v>100</v>
+      </c>
+      <c r="J62" s="11">
+        <v>100</v>
+      </c>
+      <c r="K62" s="11">
+        <v>100</v>
+      </c>
+      <c r="L62" s="11">
+        <v>100</v>
+      </c>
+      <c r="M62" s="11">
+        <v>100</v>
+      </c>
+      <c r="N62" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E63" s="3">
-        <v>100</v>
-      </c>
-      <c r="F63">
-        <v>100</v>
-      </c>
-      <c r="G63">
-        <v>100</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
+        <v>50</v>
+      </c>
+      <c r="E63" s="16">
+        <v>100</v>
+      </c>
+      <c r="F63" s="11">
+        <v>100</v>
+      </c>
+      <c r="G63" s="11">
+        <v>100</v>
+      </c>
+      <c r="H63" s="11">
+        <v>0</v>
+      </c>
+      <c r="I63" s="11">
+        <v>0</v>
+      </c>
+      <c r="J63" s="11">
         <v>20</v>
       </c>
-      <c r="K63">
+      <c r="K63" s="11">
         <v>50</v>
       </c>
-      <c r="L63">
+      <c r="L63" s="11">
         <v>50</v>
       </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
+      <c r="M63" s="11">
+        <v>0</v>
+      </c>
+      <c r="N63" s="11">
+        <v>0</v>
+      </c>
+      <c r="O63" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E64" s="3">
-        <v>80</v>
-      </c>
-      <c r="F64">
-        <v>100</v>
-      </c>
-      <c r="G64">
-        <v>100</v>
-      </c>
-      <c r="H64">
-        <v>100</v>
-      </c>
-      <c r="I64">
+        <v>100</v>
+      </c>
+      <c r="F64" s="11">
+        <v>100</v>
+      </c>
+      <c r="G64" s="11">
+        <v>100</v>
+      </c>
+      <c r="H64" s="11">
+        <v>100</v>
+      </c>
+      <c r="I64" s="11">
         <v>30</v>
       </c>
-      <c r="J64">
+      <c r="J64" s="11">
         <v>50</v>
       </c>
-      <c r="K64">
-        <v>100</v>
-      </c>
-      <c r="L64">
-        <v>100</v>
-      </c>
-      <c r="M64">
-        <v>100</v>
-      </c>
-      <c r="N64">
+      <c r="K64" s="11">
+        <v>100</v>
+      </c>
+      <c r="L64" s="11">
+        <v>100</v>
+      </c>
+      <c r="M64" s="11">
+        <v>100</v>
+      </c>
+      <c r="N64" s="11">
+        <v>0</v>
+      </c>
+      <c r="O64" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F65" t="s">
-        <v>22</v>
-      </c>
-      <c r="G65" t="s">
-        <v>22</v>
-      </c>
-      <c r="H65" t="s">
-        <v>22</v>
-      </c>
-      <c r="I65" t="s">
-        <v>22</v>
-      </c>
-      <c r="J65" t="s">
-        <v>22</v>
-      </c>
-      <c r="K65" t="s">
-        <v>22</v>
-      </c>
-      <c r="L65" t="s">
-        <v>22</v>
-      </c>
-      <c r="M65" t="s">
-        <v>22</v>
-      </c>
-      <c r="N65" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N65" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E66" s="3">
         <v>90</v>
       </c>
-      <c r="F66">
-        <v>100</v>
-      </c>
-      <c r="G66">
-        <v>100</v>
-      </c>
-      <c r="H66">
+      <c r="F66" s="11">
+        <v>100</v>
+      </c>
+      <c r="G66" s="11">
+        <v>100</v>
+      </c>
+      <c r="H66" s="11">
         <v>50</v>
       </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
+      <c r="I66" s="11">
+        <v>0</v>
+      </c>
+      <c r="J66" s="11">
         <v>25</v>
       </c>
-      <c r="K66">
-        <v>100</v>
-      </c>
-      <c r="L66">
+      <c r="K66" s="11">
+        <v>100</v>
+      </c>
+      <c r="L66" s="11">
         <v>50</v>
       </c>
-      <c r="M66">
+      <c r="M66" s="11">
         <v>50</v>
       </c>
-      <c r="N66">
+      <c r="N66" s="11">
         <v>20</v>
       </c>
-      <c r="O66">
+      <c r="O66" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E67" s="3">
         <v>90</v>
       </c>
-      <c r="F67">
-        <v>100</v>
-      </c>
-      <c r="G67">
-        <v>100</v>
-      </c>
-      <c r="H67">
+      <c r="F67" s="11">
+        <v>100</v>
+      </c>
+      <c r="G67" s="11">
+        <v>100</v>
+      </c>
+      <c r="H67" s="11">
         <v>50</v>
       </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>100</v>
-      </c>
-      <c r="L67">
+      <c r="I67" s="11">
+        <v>0</v>
+      </c>
+      <c r="J67" s="11">
+        <v>0</v>
+      </c>
+      <c r="K67" s="11">
+        <v>100</v>
+      </c>
+      <c r="L67" s="11">
         <v>50</v>
       </c>
-      <c r="M67">
+      <c r="M67" s="11">
         <v>30</v>
       </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
+      <c r="N67" s="11">
+        <v>0</v>
+      </c>
+      <c r="O67" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E68" s="3">
         <v>80</v>
       </c>
-      <c r="F68">
-        <v>100</v>
-      </c>
-      <c r="G68">
-        <v>100</v>
-      </c>
-      <c r="H68">
+      <c r="F68" s="11">
+        <v>100</v>
+      </c>
+      <c r="G68" s="11">
+        <v>100</v>
+      </c>
+      <c r="H68" s="11">
         <v>80</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="11">
         <v>80</v>
       </c>
-      <c r="J68">
+      <c r="J68" s="11">
         <v>80</v>
       </c>
-      <c r="K68">
-        <v>100</v>
-      </c>
-      <c r="L68">
-        <v>100</v>
-      </c>
-      <c r="M68">
+      <c r="K68" s="11">
+        <v>100</v>
+      </c>
+      <c r="L68" s="11">
+        <v>100</v>
+      </c>
+      <c r="M68" s="11">
         <v>80</v>
       </c>
-      <c r="N68">
+      <c r="N68" s="11">
         <v>80</v>
       </c>
-      <c r="O68">
+      <c r="O68" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -6211,6 +6202,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Demogivenby xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <DemoBy xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Comments0 xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <TaxCatchAll xmlns="5624914c-2aad-4993-a320-2eb67911e80a" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <ZoomPassword xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Demodate xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <JiraTicket xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Comments xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <TicketNumbers xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+    <Demodated xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6219,7 +6233,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020CF8294E4C5A44CB8AF60CE499E006F" ma:contentTypeVersion="32" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="009ade30d862eccbd4a375ee527febd2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="5624914c-2aad-4993-a320-2eb67911e80a" xmlns:ns3="41fb0f91-a3b9-4963-8e6c-81696287e595" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a2a584ab283d97548660d8e8b35cff3" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6565,30 +6579,19 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Demogivenby xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <DemoBy xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <Comments0 xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <TaxCatchAll xmlns="5624914c-2aad-4993-a320-2eb67911e80a" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <ZoomPassword xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Demodate xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <JiraTicket xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <Comments xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <TicketNumbers xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-    <Demodated xmlns="41fb0f91-a3b9-4963-8e6c-81696287e595" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF7AA70-C622-4509-9661-E5AB3E79D417}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="41fb0f91-a3b9-4963-8e6c-81696287e595"/>
+    <ds:schemaRef ds:uri="5624914c-2aad-4993-a320-2eb67911e80a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DABEB6D-3BAD-47AB-9B08-E3D505D0C37F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -6596,7 +6599,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{062249BE-4AA3-4403-8E45-C85EF69B7519}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6614,16 +6617,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF7AA70-C622-4509-9661-E5AB3E79D417}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="41fb0f91-a3b9-4963-8e6c-81696287e595"/>
-    <ds:schemaRef ds:uri="5624914c-2aad-4993-a320-2eb67911e80a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>